--- a/src/publish/data.xlsx
+++ b/src/publish/data.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bayer\Bayer.LoadData\Bayer.LoadODSData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E964C99-0B1C-42F8-A80F-A112ED4F9B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A4E1B5-2A1E-4ECD-8FD9-A9F18622BBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B258FCD-D826-42E0-B321-CB971A01F84A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$B$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$F$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$B$1:$B$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="485">
   <si>
     <t>Mapped Application Service 1</t>
   </si>
@@ -254,9 +256,6 @@
     <t>Important</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>On</t>
   </si>
   <si>
@@ -335,9 +334,6 @@
     <t>10.56.32.46</t>
   </si>
   <si>
-    <t>xbyqa070tf76.local</t>
-  </si>
-  <si>
     <t>90650fcea6e6bed03ce60a21d660ea2a</t>
   </si>
   <si>
@@ -359,9 +355,6 @@
     <t>0000-0000-0900-6226-1388-3982-01</t>
   </si>
   <si>
-    <t>bay_sca, BAY_CTH_CDN_Testing_Cloud, VOPS_DEV_LIN_02, VOPS_DEV_LIN_ImageOS_RHEL_8.10_standard, VOPS_DEV_LIN_ImageOS_RHEL_8:, VOPS_DEV_LIN_ImageOS_RHEL_8.10_SAP, VOPS_DEV_LINUX, VOPS_DEV_LIN_RepoScan_Ring0</t>
-  </si>
-  <si>
     <t>10.56.49.9</t>
   </si>
   <si>
@@ -404,9 +397,6 @@
     <t>BYQA070G7PI</t>
   </si>
   <si>
-    <t>Redhat</t>
-  </si>
-  <si>
     <t>BYRSI70850184</t>
   </si>
   <si>
@@ -431,9 +421,6 @@
     <t>BYQA070ZS6N</t>
   </si>
   <si>
-    <t>Sles</t>
-  </si>
-  <si>
     <t>BYRSI70850177</t>
   </si>
   <si>
@@ -623,15 +610,9 @@
     <t>VMware-42 2c a4 30 c3 46 70 f2-35 4b 9f aa 54 91 85 fe</t>
   </si>
   <si>
-    <t>CAP_CG_CCP, CAP_CT_Linux_PrivateCloud_Dev, VOPS_DEV</t>
-  </si>
-  <si>
     <t>10.33.100.243</t>
   </si>
   <si>
-    <t>byde941i57r.bayer.cnb</t>
-  </si>
-  <si>
     <t>9a91b952b86a3a10327d9ddb127050e4</t>
   </si>
   <si>
@@ -680,9 +661,6 @@
     <t>10.33.100.244</t>
   </si>
   <si>
-    <t>byde10023zaw.bayer.cnb</t>
-  </si>
-  <si>
     <t>9f91bd52b46a3a104863a32ec2aff637</t>
   </si>
   <si>
@@ -704,9 +682,6 @@
     <t>10.30.1.76</t>
   </si>
   <si>
-    <t>byde959naqy.bayer.cnb</t>
-  </si>
-  <si>
     <t>7498a38732217e109bf4eb9a991fa66e</t>
   </si>
   <si>
@@ -728,9 +703,6 @@
     <t>10.30.1.80</t>
   </si>
   <si>
-    <t>byde959da36.bayer.cnb</t>
-  </si>
-  <si>
     <t>ac8723472e65b290bcd24a49480e1ded</t>
   </si>
   <si>
@@ -857,9 +829,6 @@
     <t>0000-0007-9802-4846-7854-6749-06</t>
   </si>
   <si>
-    <t>VOPS_DEV_MANAGED_CI</t>
-  </si>
-  <si>
     <t>10.56.32.42</t>
   </si>
   <si>
@@ -995,9 +964,6 @@
     <t>XBYQA070MQHU</t>
   </si>
   <si>
-    <t>Ubuntu</t>
-  </si>
-  <si>
     <t>BYRSI70819337</t>
   </si>
   <si>
@@ -1052,9 +1018,6 @@
     <t>10.56.32.41</t>
   </si>
   <si>
-    <t>xbyqa070qkim.local</t>
-  </si>
-  <si>
     <t>a265c302fe2abed0633dba3a2767fa67</t>
   </si>
   <si>
@@ -1068,6 +1031,471 @@
   </si>
   <si>
     <t>91de4f2ca7b03e51b8c62a9fe4d1bc37</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>IT_AO_ITSM_SA20-ChangeManagement-TLSME_Approver</t>
+  </si>
+  <si>
+    <t>Public Cloud</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070WR4E</t>
+  </si>
+  <si>
+    <t>7c9e40a2cda6f690673bce5531c20c53</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>byqa070eikr</t>
+  </si>
+  <si>
+    <t>Oracle Linux Server Release 8.10</t>
+  </si>
+  <si>
+    <t>89296224-be1b-4d47-94d4-9fb77c152d23</t>
+  </si>
+  <si>
+    <t>BYRSI71438466</t>
+  </si>
+  <si>
+    <t>0000-0009-8835-3876-7189-0691-27</t>
+  </si>
+  <si>
+    <t>CAP_CG_CCP, CAP_CT_Linux_PublicCloud_Dev, VOPS_DEV_MANAGED_CI, VOPS_DEV_MANAGED_CI_LIN</t>
+  </si>
+  <si>
+    <t>10.56.32.61</t>
+  </si>
+  <si>
+    <t>byqa070eikr.bayer.cnb</t>
+  </si>
+  <si>
+    <t>c0e81419b6c7fed06353a99e19f919ef</t>
+  </si>
+  <si>
+    <t>BYQA070EIKR</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070EIKR</t>
+  </si>
+  <si>
+    <t>08e8141906c7fed0edcc908a5b70d2ed</t>
+  </si>
+  <si>
+    <t>Vertical</t>
+  </si>
+  <si>
+    <t>DE/AVS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ApplicationID: BEAT04079742, RequestID: </t>
+  </si>
+  <si>
+    <t>BYDE959DA36.bayer.cnb</t>
+  </si>
+  <si>
+    <t>Private Cloud AVS</t>
+  </si>
+  <si>
+    <t>Patch-WK10_Prod_Batch-22_Sat</t>
+  </si>
+  <si>
+    <t>vCenter@10.33.0.2</t>
+  </si>
+  <si>
+    <t>41ba4e933bad36104aac039aa4e45abf</t>
+  </si>
+  <si>
+    <t>CAP_CG_CCP, CAP_CT_Linux_PrivateCloud_Dev, VOPS_DEV_MANAGED_CI, VOPS_DEV</t>
+  </si>
+  <si>
+    <t>BYDE941I57R.bayer.cnb</t>
+  </si>
+  <si>
+    <t>Patch-WK1_NonProd_Batch-1_Mon</t>
+  </si>
+  <si>
+    <t>vCenter@10.33.16.2</t>
+  </si>
+  <si>
+    <t>03e3874a3b62be5052206a54c3e45a01</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>VDD test workload</t>
+  </si>
+  <si>
+    <t>xbyqa070qkim.bayer.cnb</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/XBYQA070QKIM</t>
+  </si>
+  <si>
+    <t>e665c302822abed0b2be6d9501a8a165</t>
+  </si>
+  <si>
+    <t>byqa0705m2t</t>
+  </si>
+  <si>
+    <t>Red Hat Enterprise Linux Server release 7.9 (Maipo)</t>
+  </si>
+  <si>
+    <t>0000-0013-0721-2833-4423-3440-57</t>
+  </si>
+  <si>
+    <t>CAP_CG_CCP</t>
+  </si>
+  <si>
+    <t>byqa0705m2t.bayer.cnb</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA0705M2T</t>
+  </si>
+  <si>
+    <t>fe9e48a2c6a6f690229a329833ff23f7</t>
+  </si>
+  <si>
+    <t>CAP_CG_CCP, bay_sca, BAY_CTH_CDN_Testing_Cloud, VOPS_DEV_LIN_02, VOPS_DEV_LIN_ImageOS_RHEL_8.10_standard, VOPS_DEV_LIN_ImageOS_RHEL_8:, VOPS_DEV_LIN_ImageOS_RHEL_8.10_SAP, VOPS_DEV_LINUX, VOPS_DEV_LIN_RepoScan_Ring0, { "TagName": "CustomTag" }, DummyTag, VOPS_DEV_PDEP_Lin_Opt_01, VOPS_DEV_LIN, VOPS_DEV_PDEP_Lin_Opt_02</t>
+  </si>
+  <si>
+    <t>/subscriptions/12fa6898-224c-4ebf-baed-86171244b259/resourceGroups/patching-sandbox-rg/providers/Microsoft.Compute/virtualMachines/patchsandvml01</t>
+  </si>
+  <si>
+    <t>be67485d3579fe1050367f618fe2cff4</t>
+  </si>
+  <si>
+    <t>byqa070zs6n</t>
+  </si>
+  <si>
+    <t>SUSE Linux Enterprise Server 15 SP2</t>
+  </si>
+  <si>
+    <t>0000-0003-3155-4921-4755-6048-46</t>
+  </si>
+  <si>
+    <t>byqa070zs6n.bayer.cnb</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070ZS6N</t>
+  </si>
+  <si>
+    <t>44ae00e2c4a6f6907bdd6224ba34d411</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/XBYQA070HYGM</t>
+  </si>
+  <si>
+    <t>1de6ccd562f5be107b3fafb3e1f0625b</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/RG-BAPU-QA-AZ-A76C4B70FD35-WORKLOAD/providers/Microsoft.Compute/virtualMachines/XBYQA0707AW4</t>
+  </si>
+  <si>
+    <t>199b79f160eaf650bd6cf9ba870048f5</t>
+  </si>
+  <si>
+    <t>ApplicationID: BEAT04079742, RequestID: f201bef6fb6972d084d2fc628eefdcec,MappedApplicationID: BYRSI55345607, MappedApplicationName: VOPs Testing Workloads_Prod, RequestedFor: EBNCY, RequestedBy: Florian Lierenfeld, ApprovedBy: Rama Tota</t>
+  </si>
+  <si>
+    <t>BYDE959NAQY.bayer.cnb</t>
+  </si>
+  <si>
+    <t>Patch-WK1_Prod_Batch-1_Sat</t>
+  </si>
+  <si>
+    <t>c69ace9f3b21b694df30e06765e45adf</t>
+  </si>
+  <si>
+    <t>byqa070cs00</t>
+  </si>
+  <si>
+    <t>Oracle Linux Server Release 9.5</t>
+  </si>
+  <si>
+    <t>30d9a9c0-2623-411a-a61e-419607bdc2a9</t>
+  </si>
+  <si>
+    <t>BYRSI71616442</t>
+  </si>
+  <si>
+    <t>0000-0003-5200-3122-6505-4128-90</t>
+  </si>
+  <si>
+    <t>10.56.32.55</t>
+  </si>
+  <si>
+    <t>byqa070cs00.local</t>
+  </si>
+  <si>
+    <t>dc8b5823700b765006990e7c2c692a93</t>
+  </si>
+  <si>
+    <t>BYQA070CS00</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070CS00</t>
+  </si>
+  <si>
+    <t>148b5823110b7650fed047a79e34ab92</t>
+  </si>
+  <si>
+    <t>/subscriptions/12fa6898-224c-4ebf-baed-86171244b259/resourceGroups/patching-sandbox-rg/providers/Microsoft.Compute/virtualMachines/patchsandvml03</t>
+  </si>
+  <si>
+    <t>77674c5d8f79fe1073f15ac9045a69c0</t>
+  </si>
+  <si>
+    <t>byqa070x0r8</t>
+  </si>
+  <si>
+    <t>0000-0001-6428-0095-4976-1922-72</t>
+  </si>
+  <si>
+    <t>byqa070x0r8.bayer.cnb</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070X0R8</t>
+  </si>
+  <si>
+    <t>3478d13228a6b214d9409507fe79f45c</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070UL90</t>
+  </si>
+  <si>
+    <t>4c78ddfe0666b21451cef0ad286e4e70</t>
+  </si>
+  <si>
+    <t>xbyqa070tf76.bayer.cnb</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/XBYQA070TF76</t>
+  </si>
+  <si>
+    <t>d4650fce97e6bed0c25377add647b528</t>
+  </si>
+  <si>
+    <t>CAP_CT_Linux_PublicCloud_Dev, VOPS_DEV, TAN-PYTHON</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070TPVN</t>
+  </si>
+  <si>
+    <t>619e04a2a6a6f690dcdd0cbe5719f175</t>
+  </si>
+  <si>
+    <t>"smart-auto smart-cloud"</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/XBYQA0705BET</t>
+  </si>
+  <si>
+    <t>069bf9f1a2eaf650fc659f874fd773b9</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/RG-BAPU-QA-AZ-A76C4B70FD35-WORKLOAD/providers/Microsoft.Compute/virtualMachines/XBYQA0700IZ7</t>
+  </si>
+  <si>
+    <t>f4e60cd55ef5be1025cf76257b5ac5aa</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA0709OHY</t>
+  </si>
+  <si>
+    <t>149ecc6248a6f690b8d8e7822ed53d29</t>
+  </si>
+  <si>
+    <t>ApplicationID: BEAT04079742, RequestID: d744bdce3ba2b2d0001eda1c95e45a97,MappedApplicationID: BYRSI55345608, MappedApplicationName: VOPs Testing Workloads_Dev, RequestedFor: ELNCL, RequestedBy: Zaheer Laher, ApprovedBy: Michael Cook</t>
+  </si>
+  <si>
+    <t>BYDE10023ZAW.bayer.cnb</t>
+  </si>
+  <si>
+    <t>Patch-WK1_NonProd_Batch-1_Thr</t>
+  </si>
+  <si>
+    <t>47e3874a3b62be5052206a54c3e45a24</t>
+  </si>
+  <si>
+    <t>xbyqa070mqhu</t>
+  </si>
+  <si>
+    <t>Ubuntu 20.04.6 Lts</t>
+  </si>
+  <si>
+    <t>0000-0002-3918-6184-4921-9605-99</t>
+  </si>
+  <si>
+    <t>xbyqa070mqhu.bayer.cnb</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/XBYQA070MQHU</t>
+  </si>
+  <si>
+    <t>cf650702482abed09eee380159e1af58</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/XBYQA0703U2X</t>
+  </si>
+  <si>
+    <t>f59bb9f185eaf650db41155de0ecb4fc</t>
+  </si>
+  <si>
+    <t>/subscriptions/12fa6898-224c-4ebf-baed-86171244b259/resourceGroups/patching-sandbox-rg/providers/Microsoft.Compute/virtualMachines/patchsandvmw02</t>
+  </si>
+  <si>
+    <t>5977c09d9d79fe104049fbb7840caeb9</t>
+  </si>
+  <si>
+    <t>byqa070g7pi</t>
+  </si>
+  <si>
+    <t>Red Hat Enterprise Linux Server release 6.10 (Santiago)</t>
+  </si>
+  <si>
+    <t>0000-0014-7643-1306-4771-6362-02</t>
+  </si>
+  <si>
+    <t>byqa070g7pi.bayer.cnb</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070G7PI</t>
+  </si>
+  <si>
+    <t>34ae80e29da6f6904ede06ff2183ed34</t>
+  </si>
+  <si>
+    <t>/subscriptions/12fa6898-224c-4ebf-baed-86171244b259/resourceGroups/patching-sandbox-rg/providers/Microsoft.Compute/virtualMachines/patchsandvmw01</t>
+  </si>
+  <si>
+    <t>f477409d8979fe10aa82cea08efb75cc</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA070FIE9</t>
+  </si>
+  <si>
+    <t>a79e4ca2f4a6f6903bd55e51a11034ee</t>
+  </si>
+  <si>
+    <t>byqa0702b7z</t>
+  </si>
+  <si>
+    <t>8a8c77a2-af7f-45ef-b8aa-2228a38fd92b</t>
+  </si>
+  <si>
+    <t>BYRSI71616445</t>
+  </si>
+  <si>
+    <t>0000-0009-9834-8601-4586-3080-79</t>
+  </si>
+  <si>
+    <t>10.56.32.53</t>
+  </si>
+  <si>
+    <t>byqa0702b7z.local</t>
+  </si>
+  <si>
+    <t>b48b9c23f10b76501bac8b78900367da</t>
+  </si>
+  <si>
+    <t>BYQA0702B7Z</t>
+  </si>
+  <si>
+    <t>/subscriptions/a76c4b70-fd35-4481-962a-e10b1e72da25/resourceGroups/rg-bapu-qa-az-a76c4b70fd35-workload/providers/Microsoft.Compute/virtualMachines/BYQA0702B7Z</t>
+  </si>
+  <si>
+    <t>f88b9c23110b765046072b96dc3761d8</t>
+  </si>
+  <si>
+    <t>/subscriptions/12fa6898-224c-4ebf-baed-86171244b259/resourceGroups/patching-sandbox-rg/providers/Microsoft.Compute/virtualMachines/patchsandvml02</t>
+  </si>
+  <si>
+    <t>5367c85d3179fe107813ac1736f53dc5</t>
+  </si>
+  <si>
+    <t>byde941uik5</t>
+  </si>
+  <si>
+    <t>BYRSI71765409</t>
+  </si>
+  <si>
+    <t>VMware-42 2c 37 75 21 64 17 1f-f5 63 d8 3e b6 71 dc 0f</t>
+  </si>
+  <si>
+    <t>CAP_CG_CCP, CAP_CT_Windows_PrivateCloud_Dev</t>
+  </si>
+  <si>
+    <t>10.30.87.33</t>
+  </si>
+  <si>
+    <t>byde941uik5.bayer.cnb</t>
+  </si>
+  <si>
+    <t>2dfcb0515d9fba94306ee4c7104524fd</t>
+  </si>
+  <si>
+    <t>BYDE941UIK5</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>MSP_CMDB_ImportSet</t>
+  </si>
+  <si>
+    <t>SDC20_TL_SME_Change_Approvers</t>
+  </si>
+  <si>
+    <t>IT_INFRA_CLS_WINDOWS_OPS</t>
+  </si>
+  <si>
+    <t>a5905b8f3b033ad0298c4e2eb3e45a07</t>
+  </si>
+  <si>
+    <t>byde941yxk6</t>
+  </si>
+  <si>
+    <t>Windows Server 2016 Datacenter</t>
+  </si>
+  <si>
+    <t>BYRSI71765403</t>
+  </si>
+  <si>
+    <t>VMware-42 2c 0c 2c fa 46 d1 ce-e0 30 4d 29 2e 9b b6 3c</t>
+  </si>
+  <si>
+    <t>10.30.87.56</t>
+  </si>
+  <si>
+    <t>byde941yxk6.bayer.cnb</t>
+  </si>
+  <si>
+    <t>50fcb8dd945fba946008666cf6ca90e2</t>
+  </si>
+  <si>
+    <t>BYDE941YXK6</t>
+  </si>
+  <si>
+    <t>15901b8f3b033ad0298c4e2eb3e45a5b</t>
+  </si>
+  <si>
+    <t>Proposed patch window</t>
+  </si>
+  <si>
+    <t>vCenter Reference</t>
+  </si>
+  <si>
+    <t>Subscription</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AF9D5F-633B-4593-A18F-1065DF67794C}">
-  <dimension ref="A1:CL27"/>
+  <dimension ref="A1:CP32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.5546875" customWidth="1"/>
@@ -1457,9 +1885,15 @@
     <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.33203125" customWidth="1"/>
     <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" customWidth="1"/>
+    <col min="7" max="8" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.77734375" customWidth="1"/>
-    <col min="18" max="18" width="21" customWidth="1"/>
+    <col min="18" max="19" width="35.109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="31.77734375" bestFit="1" customWidth="1"/>
@@ -1470,28 +1904,43 @@
     <col min="27" max="27" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="47.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="35.88671875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="20.21875" customWidth="1"/>
     <col min="40" max="40" width="47.44140625" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="45.109375" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="49.5546875" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="34.21875" customWidth="1"/>
-    <col min="89" max="89" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="33.6640625" customWidth="1"/>
+    <col min="66" max="66" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="34.21875" customWidth="1"/>
+    <col min="69" max="69" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="75" max="76" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="33.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:94" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1551,7 +2000,7 @@
         <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W1" t="s">
         <v>21</v>
@@ -1602,7 +2051,7 @@
         <v>20</v>
       </c>
       <c r="AM1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AN1" t="s">
         <v>29</v>
@@ -1677,93 +2126,108 @@
         <v>44</v>
       </c>
       <c r="BL1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="BM1" t="s">
+        <v>482</v>
+      </c>
+      <c r="BN1" t="s">
         <v>21</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>45</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>1</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>2</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>3</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>46</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>23</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>24</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>7</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>25</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>8</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>9</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>11</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>47</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>48</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>12</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>13</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>49</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>50</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>51</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>28</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>37</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>39</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>52</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
+        <v>483</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>484</v>
+      </c>
+      <c r="CN1" t="s">
         <v>4</v>
       </c>
-      <c r="CL1" t="s">
-        <v>74</v>
+      <c r="CO1" t="s">
+        <v>177</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>266</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>330</v>
       </c>
       <c r="D2" t="s">
         <v>53</v>
@@ -1772,16 +2236,16 @@
         <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="G2" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="J2" t="s">
         <v>55</v>
@@ -1798,8 +2262,11 @@
       <c r="N2" t="s">
         <v>58</v>
       </c>
+      <c r="O2" t="s">
+        <v>331</v>
+      </c>
       <c r="P2" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="Q2" t="s">
         <v>59</v>
@@ -1817,13 +2284,13 @@
         <v>62</v>
       </c>
       <c r="V2" t="s">
-        <v>187</v>
+        <v>268</v>
       </c>
       <c r="W2" t="s">
         <v>63</v>
       </c>
       <c r="X2" t="s">
-        <v>188</v>
+        <v>269</v>
       </c>
       <c r="Y2" t="s">
         <v>64</v>
@@ -1835,31 +2302,34 @@
         <v>54</v>
       </c>
       <c r="AB2" s="1">
-        <v>46073.489861111113</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE2" t="s">
         <v>64</v>
       </c>
       <c r="AF2" t="s">
         <v>64</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>330</v>
       </c>
       <c r="AH2" t="s">
         <v>66</v>
       </c>
       <c r="AI2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ2">
         <v>9.6</v>
       </c>
       <c r="AK2" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="AL2" t="s">
         <v>67</v>
@@ -1868,73 +2338,88 @@
         <v>68</v>
       </c>
       <c r="AN2" t="s">
-        <v>191</v>
+        <v>270</v>
       </c>
       <c r="AO2" t="s">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AR2" t="s">
         <v>70</v>
       </c>
+      <c r="AS2">
+        <v>64</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>331</v>
+      </c>
       <c r="AW2" t="s">
-        <v>188</v>
+        <v>269</v>
       </c>
       <c r="AX2" t="s">
-        <v>192</v>
+        <v>271</v>
       </c>
       <c r="AZ2" s="2">
-        <v>3623</v>
+        <v>3655</v>
       </c>
       <c r="BA2" t="s">
-        <v>193</v>
+        <v>272</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>202</v>
       </c>
       <c r="BD2" t="s">
-        <v>194</v>
+        <v>85</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>202</v>
       </c>
       <c r="BG2" t="s">
-        <v>195</v>
+        <v>273</v>
       </c>
       <c r="BI2" t="s">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="BJ2" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK2" t="b">
         <v>1</v>
       </c>
       <c r="BL2" t="s">
-        <v>197</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>198</v>
+        <v>275</v>
       </c>
       <c r="BN2" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="BO2" t="s">
+        <v>276</v>
+      </c>
+      <c r="BP2" t="s">
         <v>64</v>
       </c>
       <c r="BQ2" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR2" t="s">
         <v>53</v>
       </c>
-      <c r="BR2" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS2" s="1">
-        <v>46072.834317129629</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>200</v>
+      <c r="BS2" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT2" s="1">
+        <v>46089.31527777778</v>
       </c>
       <c r="BU2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="BV2" t="s">
         <v>64</v>
@@ -1943,36 +2428,51 @@
         <v>64</v>
       </c>
       <c r="BX2" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY2" t="s">
         <v>66</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BZ2" t="s">
         <v>70</v>
       </c>
-      <c r="BZ2">
-        <v>114</v>
-      </c>
       <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CE2">
         <v>2</v>
       </c>
-      <c r="CD2">
-        <v>2</v>
-      </c>
-      <c r="CF2" s="2">
+      <c r="CG2" s="2">
         <v>4096</v>
       </c>
+      <c r="CJ2" t="s">
+        <v>204</v>
+      </c>
       <c r="CK2" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>340</v>
+        <v>270</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>334</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>335</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>328</v>
       </c>
     </row>
-    <row r="3" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>179</v>
+      </c>
+      <c r="C3" t="s">
+        <v>336</v>
       </c>
       <c r="D3" t="s">
         <v>53</v>
@@ -1981,16 +2481,16 @@
         <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J3" t="s">
         <v>55</v>
@@ -2007,8 +2507,11 @@
       <c r="N3" t="s">
         <v>58</v>
       </c>
+      <c r="O3" t="s">
+        <v>331</v>
+      </c>
       <c r="P3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="Q3" t="s">
         <v>59</v>
@@ -2026,13 +2529,13 @@
         <v>62</v>
       </c>
       <c r="V3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="W3" t="s">
         <v>63</v>
       </c>
       <c r="X3" t="s">
-        <v>204</v>
+        <v>337</v>
       </c>
       <c r="Y3" t="s">
         <v>64</v>
@@ -2044,124 +2547,124 @@
         <v>54</v>
       </c>
       <c r="AB3" s="1">
-        <v>46073.491423611114</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC3" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD3" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE3" t="s">
         <v>64</v>
       </c>
       <c r="AF3" t="s">
         <v>64</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>336</v>
       </c>
       <c r="AH3" t="s">
         <v>66</v>
       </c>
       <c r="AI3" t="s">
-        <v>205</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>206</v>
+        <v>338</v>
+      </c>
+      <c r="AJ3">
+        <v>8.1</v>
       </c>
       <c r="AK3" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="AL3" t="s">
         <v>67</v>
       </c>
       <c r="AM3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>339</v>
+      </c>
+      <c r="AO3" t="s">
         <v>79</v>
       </c>
-      <c r="AN3" t="s">
-        <v>191</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>191</v>
-      </c>
       <c r="AP3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AR3" t="s">
         <v>70</v>
       </c>
-      <c r="AT3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>58</v>
+      <c r="AS3">
+        <v>49</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>331</v>
       </c>
       <c r="AW3" t="s">
+        <v>337</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>340</v>
+      </c>
+      <c r="AZ3" s="2">
+        <v>3623</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>341</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>342</v>
+      </c>
+      <c r="BE3" t="s">
         <v>204</v>
       </c>
-      <c r="AX3" t="s">
-        <v>207</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AZ3" s="2">
-        <v>4096</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>208</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>209</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>211</v>
-      </c>
       <c r="BF3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="BG3" t="s">
-        <v>212</v>
+        <v>343</v>
       </c>
       <c r="BI3" t="s">
-        <v>213</v>
+        <v>344</v>
       </c>
       <c r="BJ3" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>214</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>198</v>
+        <v>345</v>
       </c>
       <c r="BN3" t="s">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="BO3" t="s">
+        <v>346</v>
+      </c>
+      <c r="BP3" t="s">
         <v>64</v>
       </c>
       <c r="BQ3" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR3" t="s">
         <v>53</v>
       </c>
-      <c r="BR3" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS3" s="1">
-        <v>46072.835659722223</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>200</v>
+      <c r="BS3" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT3" s="1">
+        <v>46089.31527777778</v>
       </c>
       <c r="BU3" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="BV3" t="s">
         <v>64</v>
@@ -2170,36 +2673,57 @@
         <v>64</v>
       </c>
       <c r="BX3" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY3" t="s">
         <v>66</v>
       </c>
-      <c r="BY3" t="s">
+      <c r="BZ3" t="s">
         <v>70</v>
       </c>
-      <c r="BZ3">
-        <v>130</v>
-      </c>
       <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CC3" t="s">
+        <v>58</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>58</v>
+      </c>
+      <c r="CE3">
         <v>2</v>
       </c>
-      <c r="CD3">
-        <v>2</v>
-      </c>
-      <c r="CF3" s="2">
+      <c r="CG3" s="2">
         <v>4096</v>
       </c>
+      <c r="CJ3" t="s">
+        <v>204</v>
+      </c>
       <c r="CK3" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>340</v>
+        <v>339</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>347</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>179</v>
+      </c>
+      <c r="C4" t="s">
+        <v>336</v>
       </c>
       <c r="D4" t="s">
         <v>53</v>
@@ -2208,16 +2732,16 @@
         <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J4" t="s">
         <v>55</v>
@@ -2234,8 +2758,11 @@
       <c r="N4" t="s">
         <v>58</v>
       </c>
+      <c r="O4" t="s">
+        <v>331</v>
+      </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="Q4" t="s">
         <v>59</v>
@@ -2253,13 +2780,13 @@
         <v>62</v>
       </c>
       <c r="V4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="W4" t="s">
         <v>63</v>
       </c>
       <c r="X4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y4" t="s">
         <v>64</v>
@@ -2268,46 +2795,49 @@
         <v>53</v>
       </c>
       <c r="AA4" t="s">
-        <v>54</v>
+        <v>349</v>
       </c>
       <c r="AB4" s="1">
-        <v>46073.493032407408</v>
+        <v>46087.322916666664</v>
       </c>
       <c r="AC4" t="s">
         <v>65</v>
       </c>
       <c r="AD4" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE4" t="s">
         <v>64</v>
       </c>
       <c r="AF4" t="s">
         <v>64</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>336</v>
       </c>
       <c r="AH4" t="s">
         <v>66</v>
       </c>
       <c r="AI4" t="s">
-        <v>205</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>206</v>
+        <v>184</v>
+      </c>
+      <c r="AJ4">
+        <v>9.6</v>
       </c>
       <c r="AK4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AL4" t="s">
         <v>67</v>
       </c>
       <c r="AM4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="AN4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AO4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AP4">
         <v>2</v>
@@ -2324,71 +2854,77 @@
       <c r="AU4" t="s">
         <v>58</v>
       </c>
+      <c r="AV4" t="s">
+        <v>350</v>
+      </c>
       <c r="AW4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AX4" t="s">
         <v>216</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AZ4" s="2">
+        <v>3623</v>
+      </c>
+      <c r="BA4" t="s">
         <v>217</v>
       </c>
-      <c r="AY4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AZ4" s="2">
-        <v>8192</v>
-      </c>
-      <c r="BA4" t="s">
+      <c r="BC4" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD4" t="s">
         <v>218</v>
       </c>
-      <c r="BC4" t="s">
-        <v>209</v>
-      </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>202</v>
+      </c>
+      <c r="BG4" t="s">
         <v>219</v>
       </c>
-      <c r="BE4" t="s">
-        <v>211</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>209</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>220</v>
+      <c r="BH4" t="s">
+        <v>351</v>
       </c>
       <c r="BI4" t="s">
-        <v>221</v>
+        <v>352</v>
       </c>
       <c r="BJ4" t="s">
-        <v>71</v>
+        <v>353</v>
       </c>
       <c r="BK4" t="b">
         <v>1</v>
       </c>
       <c r="BL4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BM4" t="s">
-        <v>198</v>
+        <v>354</v>
       </c>
       <c r="BN4" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="BO4" t="s">
+        <v>221</v>
+      </c>
+      <c r="BP4" t="s">
         <v>64</v>
       </c>
       <c r="BQ4" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR4" t="s">
         <v>53</v>
       </c>
-      <c r="BR4" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS4" s="1">
-        <v>46072.83394675926</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>200</v>
+      <c r="BS4" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT4" s="1">
+        <v>46088.834027777775</v>
       </c>
       <c r="BU4" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="BV4" t="s">
         <v>64</v>
@@ -2397,36 +2933,51 @@
         <v>64</v>
       </c>
       <c r="BX4" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY4" t="s">
         <v>66</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="BZ4" t="s">
         <v>70</v>
       </c>
-      <c r="BZ4">
-        <v>280</v>
-      </c>
       <c r="CA4">
+        <v>264</v>
+      </c>
+      <c r="CB4">
         <v>2</v>
       </c>
-      <c r="CD4">
+      <c r="CE4">
         <v>2</v>
       </c>
-      <c r="CF4" s="2">
-        <v>8192</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>54</v>
+      <c r="CG4" s="2">
+        <v>4096</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>204</v>
       </c>
       <c r="CL4" t="s">
-        <v>340</v>
+        <v>355</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>356</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="5" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>179</v>
+      </c>
+      <c r="C5" t="s">
+        <v>330</v>
       </c>
       <c r="D5" t="s">
         <v>53</v>
@@ -2435,16 +2986,16 @@
         <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J5" t="s">
         <v>55</v>
@@ -2461,8 +3012,11 @@
       <c r="N5" t="s">
         <v>58</v>
       </c>
+      <c r="O5" t="s">
+        <v>331</v>
+      </c>
       <c r="P5" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="Q5" t="s">
         <v>59</v>
@@ -2480,13 +3034,13 @@
         <v>62</v>
       </c>
       <c r="V5" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="W5" t="s">
         <v>63</v>
       </c>
       <c r="X5" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="Y5" t="s">
         <v>64</v>
@@ -2498,31 +3052,34 @@
         <v>54</v>
       </c>
       <c r="AB5" s="1">
-        <v>46073.50644675926</v>
+        <v>46087.325694444444</v>
       </c>
       <c r="AC5" t="s">
         <v>65</v>
       </c>
       <c r="AD5" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE5" t="s">
         <v>64</v>
       </c>
       <c r="AF5" t="s">
         <v>64</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>330</v>
       </c>
       <c r="AH5" t="s">
         <v>66</v>
       </c>
       <c r="AI5" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ5">
         <v>9.6</v>
       </c>
       <c r="AK5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AL5" t="s">
         <v>67</v>
@@ -2531,10 +3088,10 @@
         <v>68</v>
       </c>
       <c r="AN5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AO5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AP5">
         <v>2</v>
@@ -2545,74 +3102,77 @@
       <c r="AR5" t="s">
         <v>70</v>
       </c>
-      <c r="AT5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>58</v>
+      <c r="AV5" t="s">
+        <v>350</v>
       </c>
       <c r="AW5" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="AX5" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="AZ5" s="2">
         <v>3623</v>
       </c>
       <c r="BA5" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="BC5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="BD5" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="BE5" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="BF5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="BG5" t="s">
-        <v>228</v>
+        <v>189</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>351</v>
       </c>
       <c r="BI5" t="s">
-        <v>229</v>
+        <v>358</v>
       </c>
       <c r="BJ5" t="s">
-        <v>71</v>
+        <v>353</v>
       </c>
       <c r="BK5" t="b">
         <v>1</v>
       </c>
       <c r="BL5" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="BM5" t="s">
-        <v>198</v>
+        <v>359</v>
       </c>
       <c r="BN5" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="BO5" t="s">
+        <v>192</v>
+      </c>
+      <c r="BP5" t="s">
         <v>64</v>
       </c>
       <c r="BQ5" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR5" t="s">
         <v>53</v>
       </c>
-      <c r="BR5" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS5" s="1">
-        <v>46072.834386574075</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>200</v>
+      <c r="BS5" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT5" s="1">
+        <v>46088.834027777775</v>
       </c>
       <c r="BU5" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="BV5" t="s">
         <v>64</v>
@@ -2621,36 +3181,51 @@
         <v>64</v>
       </c>
       <c r="BX5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY5" t="s">
         <v>66</v>
       </c>
-      <c r="BY5" t="s">
+      <c r="BZ5" t="s">
         <v>70</v>
       </c>
-      <c r="BZ5">
-        <v>264</v>
-      </c>
       <c r="CA5">
+        <v>114</v>
+      </c>
+      <c r="CB5">
         <v>2</v>
       </c>
-      <c r="CD5">
+      <c r="CE5">
         <v>2</v>
       </c>
-      <c r="CF5" s="2">
+      <c r="CG5" s="2">
         <v>4096</v>
       </c>
-      <c r="CK5" t="s">
-        <v>54</v>
+      <c r="CJ5" t="s">
+        <v>204</v>
       </c>
       <c r="CL5" t="s">
-        <v>340</v>
+        <v>360</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO5" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>295</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>179</v>
+      </c>
+      <c r="C6" t="s">
+        <v>362</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
@@ -2659,16 +3234,16 @@
         <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="J6" t="s">
         <v>55</v>
@@ -2677,7 +3252,7 @@
         <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="M6" t="s">
         <v>58</v>
@@ -2685,8 +3260,11 @@
       <c r="N6" t="s">
         <v>58</v>
       </c>
+      <c r="O6" t="s">
+        <v>331</v>
+      </c>
       <c r="P6" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="Q6" t="s">
         <v>59</v>
@@ -2704,13 +3282,13 @@
         <v>62</v>
       </c>
       <c r="V6" t="s">
-        <v>235</v>
+        <v>297</v>
       </c>
       <c r="W6" t="s">
         <v>63</v>
       </c>
       <c r="X6" t="s">
-        <v>236</v>
+        <v>319</v>
       </c>
       <c r="Y6" t="s">
         <v>64</v>
@@ -2722,10 +3300,10 @@
         <v>54</v>
       </c>
       <c r="AB6" s="1">
-        <v>46073.492268518516</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC6" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD6" t="s">
         <v>64</v>
@@ -2735,100 +3313,115 @@
       </c>
       <c r="AF6" t="s">
         <v>64</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>362</v>
       </c>
       <c r="AH6" t="s">
         <v>66</v>
       </c>
       <c r="AI6" t="s">
-        <v>237</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>206</v>
+        <v>320</v>
+      </c>
+      <c r="AJ6">
+        <v>22.04</v>
       </c>
       <c r="AK6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL6" t="s">
         <v>67</v>
       </c>
       <c r="AM6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>321</v>
+      </c>
+      <c r="AO6" t="s">
         <v>79</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>238</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>80</v>
       </c>
       <c r="AP6">
         <v>1</v>
       </c>
       <c r="AQ6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR6" t="s">
         <v>70</v>
       </c>
       <c r="AS6">
-        <v>128</v>
+        <v>54</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>331</v>
       </c>
       <c r="AW6" t="s">
-        <v>236</v>
+        <v>319</v>
       </c>
       <c r="AX6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AZ6" s="2">
-        <v>8191</v>
+        <v>3914</v>
       </c>
       <c r="BA6" t="s">
-        <v>240</v>
+        <v>323</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>202</v>
       </c>
       <c r="BD6" t="s">
-        <v>241</v>
+        <v>85</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>202</v>
       </c>
       <c r="BG6" t="s">
-        <v>242</v>
+        <v>324</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>363</v>
       </c>
       <c r="BI6" t="s">
-        <v>243</v>
+        <v>364</v>
       </c>
       <c r="BJ6" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK6" t="b">
         <v>1</v>
       </c>
       <c r="BL6" t="s">
-        <v>244</v>
-      </c>
-      <c r="BM6" t="s">
+        <v>325</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>326</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>362</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT6" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU6" t="s">
         <v>83</v>
       </c>
-      <c r="BN6" t="s">
-        <v>245</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ6" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS6" s="1">
-        <v>46068.311215277776</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>64</v>
-      </c>
       <c r="BV6" t="s">
         <v>64</v>
       </c>
@@ -2836,36 +3429,51 @@
         <v>64</v>
       </c>
       <c r="BX6" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY6" t="s">
         <v>66</v>
       </c>
-      <c r="BY6" t="s">
+      <c r="BZ6" t="s">
         <v>70</v>
       </c>
-      <c r="BZ6">
+      <c r="CA6">
         <v>0</v>
       </c>
-      <c r="CD6">
+      <c r="CE6">
         <v>2</v>
       </c>
-      <c r="CF6" s="2">
-        <v>8192</v>
+      <c r="CG6" s="2">
+        <v>4096</v>
       </c>
       <c r="CJ6" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="CK6" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL6" t="s">
-        <v>342</v>
+        <v>321</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>365</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>366</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="7" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>330</v>
       </c>
       <c r="D7" t="s">
         <v>53</v>
@@ -2874,16 +3482,16 @@
         <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s">
         <v>55</v>
@@ -2900,8 +3508,11 @@
       <c r="N7" t="s">
         <v>58</v>
       </c>
+      <c r="O7" t="s">
+        <v>331</v>
+      </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>149</v>
       </c>
       <c r="Q7" t="s">
         <v>59</v>
@@ -2919,13 +3530,13 @@
         <v>62</v>
       </c>
       <c r="V7" t="s">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="W7" t="s">
         <v>63</v>
       </c>
       <c r="X7" t="s">
-        <v>246</v>
+        <v>367</v>
       </c>
       <c r="Y7" t="s">
         <v>64</v>
@@ -2937,10 +3548,10 @@
         <v>54</v>
       </c>
       <c r="AB7" s="1">
-        <v>46073.494814814818</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC7" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD7" t="s">
         <v>64</v>
@@ -2950,18 +3561,21 @@
       </c>
       <c r="AF7" t="s">
         <v>64</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>330</v>
       </c>
       <c r="AH7" t="s">
         <v>66</v>
       </c>
       <c r="AI7" t="s">
-        <v>189</v>
+        <v>368</v>
       </c>
       <c r="AJ7">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="AK7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL7" t="s">
         <v>67</v>
@@ -2969,17 +3583,11 @@
       <c r="AM7" t="s">
         <v>68</v>
       </c>
-      <c r="AN7" t="s">
-        <v>247</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>80</v>
-      </c>
       <c r="AP7">
         <v>1</v>
       </c>
       <c r="AQ7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR7" t="s">
         <v>70</v>
@@ -2987,60 +3595,75 @@
       <c r="AS7">
         <v>64</v>
       </c>
+      <c r="AV7" t="s">
+        <v>331</v>
+      </c>
       <c r="AW7" t="s">
-        <v>246</v>
+        <v>367</v>
       </c>
       <c r="AX7" t="s">
-        <v>248</v>
+        <v>173</v>
       </c>
       <c r="AZ7" s="2">
-        <v>7677</v>
+        <v>3785</v>
       </c>
       <c r="BA7" t="s">
-        <v>249</v>
+        <v>369</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>202</v>
       </c>
       <c r="BD7" t="s">
-        <v>250</v>
+        <v>370</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>202</v>
       </c>
       <c r="BG7" t="s">
-        <v>251</v>
+        <v>175</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>363</v>
       </c>
       <c r="BI7" t="s">
-        <v>252</v>
+        <v>371</v>
       </c>
       <c r="BJ7" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK7" t="b">
         <v>1</v>
       </c>
       <c r="BL7" t="s">
-        <v>253</v>
-      </c>
-      <c r="BM7" t="s">
+        <v>176</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>172</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT7" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU7" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" t="s">
-        <v>254</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS7" s="1">
-        <v>46072.839074074072</v>
-      </c>
-      <c r="BT7" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>64</v>
-      </c>
       <c r="BV7" t="s">
         <v>64</v>
       </c>
@@ -3048,36 +3671,51 @@
         <v>64</v>
       </c>
       <c r="BX7" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY7" t="s">
         <v>66</v>
       </c>
-      <c r="BY7" t="s">
+      <c r="BZ7" t="s">
         <v>70</v>
       </c>
-      <c r="BZ7">
+      <c r="CA7">
         <v>0</v>
       </c>
-      <c r="CD7">
+      <c r="CE7">
         <v>2</v>
       </c>
-      <c r="CF7" s="2">
-        <v>8192</v>
+      <c r="CG7" s="2">
+        <v>4096</v>
       </c>
       <c r="CJ7" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="CK7" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL7" t="s">
-        <v>342</v>
+        <v>174</v>
+      </c>
+      <c r="CM7" t="s">
+        <v>372</v>
+      </c>
+      <c r="CN7" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO7" t="s">
+        <v>373</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="8" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>232</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>336</v>
       </c>
       <c r="D8" t="s">
         <v>53</v>
@@ -3086,16 +3724,16 @@
         <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
@@ -3112,8 +3750,11 @@
       <c r="N8" t="s">
         <v>58</v>
       </c>
+      <c r="O8" t="s">
+        <v>331</v>
+      </c>
       <c r="P8" t="s">
-        <v>234</v>
+        <v>89</v>
       </c>
       <c r="Q8" t="s">
         <v>59</v>
@@ -3131,13 +3772,13 @@
         <v>62</v>
       </c>
       <c r="V8" t="s">
-        <v>235</v>
+        <v>90</v>
       </c>
       <c r="W8" t="s">
         <v>63</v>
       </c>
       <c r="X8" t="s">
-        <v>255</v>
+        <v>99</v>
       </c>
       <c r="Y8" t="s">
         <v>64</v>
@@ -3149,31 +3790,34 @@
         <v>54</v>
       </c>
       <c r="AB8" s="1">
-        <v>46073.492488425924</v>
+        <v>46089.23333333333</v>
       </c>
       <c r="AC8" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD8" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE8" t="s">
         <v>64</v>
       </c>
       <c r="AF8" t="s">
         <v>64</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>336</v>
       </c>
       <c r="AH8" t="s">
         <v>66</v>
       </c>
       <c r="AI8" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="AJ8">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="AK8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL8" t="s">
         <v>67</v>
@@ -3182,10 +3826,10 @@
         <v>68</v>
       </c>
       <c r="AN8" t="s">
-        <v>256</v>
+        <v>101</v>
       </c>
       <c r="AO8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP8">
         <v>1</v>
@@ -3199,60 +3843,72 @@
       <c r="AS8">
         <v>256</v>
       </c>
+      <c r="AV8" t="s">
+        <v>331</v>
+      </c>
       <c r="AW8" t="s">
-        <v>255</v>
+        <v>99</v>
       </c>
       <c r="AX8" t="s">
-        <v>257</v>
+        <v>102</v>
       </c>
       <c r="AZ8" s="2">
-        <v>7682</v>
+        <v>7698</v>
       </c>
       <c r="BA8" t="s">
-        <v>258</v>
+        <v>103</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>202</v>
       </c>
       <c r="BD8" t="s">
-        <v>259</v>
+        <v>374</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>202</v>
       </c>
       <c r="BG8" t="s">
-        <v>260</v>
+        <v>104</v>
       </c>
       <c r="BI8" t="s">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="BJ8" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK8" t="b">
         <v>1</v>
       </c>
       <c r="BL8" t="s">
-        <v>262</v>
-      </c>
-      <c r="BM8" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>99</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT8" s="1">
+        <v>46089.313194444447</v>
+      </c>
+      <c r="BU8" t="s">
         <v>83</v>
       </c>
-      <c r="BN8" t="s">
-        <v>255</v>
-      </c>
-      <c r="BO8" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ8" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR8" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS8" s="1">
-        <v>46072.841099537036</v>
-      </c>
-      <c r="BT8" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>64</v>
-      </c>
       <c r="BV8" t="s">
         <v>64</v>
       </c>
@@ -3260,36 +3916,51 @@
         <v>64</v>
       </c>
       <c r="BX8" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY8" t="s">
         <v>66</v>
       </c>
-      <c r="BY8" t="s">
+      <c r="BZ8" t="s">
         <v>70</v>
       </c>
-      <c r="BZ8">
+      <c r="CA8">
         <v>16</v>
       </c>
-      <c r="CD8">
+      <c r="CE8">
         <v>2</v>
       </c>
-      <c r="CF8" s="2">
+      <c r="CG8" s="2">
         <v>8192</v>
       </c>
       <c r="CJ8" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="CK8" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL8" t="s">
-        <v>342</v>
+        <v>101</v>
+      </c>
+      <c r="CM8" t="s">
+        <v>375</v>
+      </c>
+      <c r="CN8" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO8" t="s">
+        <v>376</v>
+      </c>
+      <c r="CP8" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>263</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C9" t="s">
+        <v>362</v>
       </c>
       <c r="D9" t="s">
         <v>53</v>
@@ -3298,16 +3969,16 @@
         <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J9" t="s">
         <v>55</v>
@@ -3324,8 +3995,11 @@
       <c r="N9" t="s">
         <v>58</v>
       </c>
+      <c r="O9" t="s">
+        <v>331</v>
+      </c>
       <c r="P9" t="s">
-        <v>264</v>
+        <v>123</v>
       </c>
       <c r="Q9" t="s">
         <v>59</v>
@@ -3343,13 +4017,13 @@
         <v>62</v>
       </c>
       <c r="V9" t="s">
-        <v>265</v>
+        <v>124</v>
       </c>
       <c r="W9" t="s">
         <v>63</v>
       </c>
       <c r="X9" t="s">
-        <v>266</v>
+        <v>377</v>
       </c>
       <c r="Y9" t="s">
         <v>64</v>
@@ -3361,10 +4035,10 @@
         <v>54</v>
       </c>
       <c r="AB9" s="1">
-        <v>46073.514039351852</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC9" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD9" t="s">
         <v>64</v>
@@ -3374,100 +4048,121 @@
       </c>
       <c r="AF9" t="s">
         <v>64</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>362</v>
       </c>
       <c r="AH9" t="s">
         <v>66</v>
       </c>
       <c r="AI9" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>268</v>
+        <v>378</v>
+      </c>
+      <c r="AJ9">
+        <v>15.2</v>
       </c>
       <c r="AK9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL9" t="s">
         <v>67</v>
       </c>
       <c r="AM9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO9" t="s">
         <v>79</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>269</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>80</v>
       </c>
       <c r="AP9">
         <v>1</v>
       </c>
       <c r="AQ9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR9" t="s">
         <v>70</v>
       </c>
       <c r="AS9">
+        <v>30</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>331</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>377</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ9" s="2">
+        <v>3922</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>379</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>370</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>202</v>
+      </c>
+      <c r="BG9" t="s">
         <v>128</v>
       </c>
-      <c r="AW9" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>270</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AZ9" s="2">
-        <v>8187</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>271</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>272</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>273</v>
+      <c r="BH9" t="s">
+        <v>363</v>
       </c>
       <c r="BI9" t="s">
-        <v>274</v>
+        <v>380</v>
       </c>
       <c r="BJ9" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK9" t="b">
         <v>1</v>
       </c>
       <c r="BL9" t="s">
-        <v>275</v>
-      </c>
-      <c r="BM9" t="s">
+        <v>129</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>362</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT9" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU9" t="s">
         <v>83</v>
       </c>
-      <c r="BN9" t="s">
-        <v>276</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS9" s="1">
-        <v>46072.839062500003</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>64</v>
-      </c>
       <c r="BV9" t="s">
         <v>64</v>
       </c>
@@ -3475,36 +4170,57 @@
         <v>64</v>
       </c>
       <c r="BX9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY9" t="s">
         <v>66</v>
       </c>
-      <c r="BY9" t="s">
+      <c r="BZ9" t="s">
         <v>70</v>
       </c>
-      <c r="BZ9">
+      <c r="CA9">
         <v>0</v>
       </c>
-      <c r="CD9">
+      <c r="CC9" t="s">
+        <v>58</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>58</v>
+      </c>
+      <c r="CE9">
         <v>2</v>
       </c>
-      <c r="CF9" s="2">
-        <v>8192</v>
+      <c r="CG9" s="2">
+        <v>4096</v>
       </c>
       <c r="CJ9" t="s">
-        <v>269</v>
-      </c>
-      <c r="CK9" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL9" t="s">
-        <v>342</v>
+        <v>204</v>
+      </c>
+      <c r="CK9" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM9" t="s">
+        <v>381</v>
+      </c>
+      <c r="CN9" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO9" t="s">
+        <v>382</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="10" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>277</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>336</v>
       </c>
       <c r="D10" t="s">
         <v>53</v>
@@ -3513,16 +4229,16 @@
         <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J10" t="s">
         <v>55</v>
@@ -3539,8 +4255,11 @@
       <c r="N10" t="s">
         <v>58</v>
       </c>
+      <c r="O10" t="s">
+        <v>331</v>
+      </c>
       <c r="P10" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="Q10" t="s">
         <v>59</v>
@@ -3558,13 +4277,13 @@
         <v>62</v>
       </c>
       <c r="V10" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="W10" t="s">
         <v>63</v>
       </c>
       <c r="X10" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="Y10" t="s">
         <v>64</v>
@@ -3576,31 +4295,34 @@
         <v>54</v>
       </c>
       <c r="AB10" s="1">
-        <v>46073.491944444446</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC10" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD10" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE10" t="s">
         <v>64</v>
       </c>
       <c r="AF10" t="s">
         <v>64</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>336</v>
       </c>
       <c r="AH10" t="s">
         <v>66</v>
       </c>
       <c r="AI10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ10">
         <v>9.6</v>
       </c>
       <c r="AK10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL10" t="s">
         <v>67</v>
@@ -3609,16 +4331,16 @@
         <v>68</v>
       </c>
       <c r="AN10" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="AO10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP10">
         <v>1</v>
       </c>
       <c r="AQ10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR10" t="s">
         <v>70</v>
@@ -3626,60 +4348,72 @@
       <c r="AS10">
         <v>64</v>
       </c>
+      <c r="AV10" t="s">
+        <v>331</v>
+      </c>
       <c r="AW10" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="AX10" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="AZ10" s="2">
-        <v>3655</v>
+        <v>7677</v>
       </c>
       <c r="BA10" t="s">
-        <v>283</v>
+        <v>239</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>202</v>
       </c>
       <c r="BD10" t="s">
-        <v>86</v>
+        <v>240</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>202</v>
       </c>
       <c r="BG10" t="s">
-        <v>284</v>
+        <v>241</v>
       </c>
       <c r="BI10" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="BJ10" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK10" t="b">
         <v>1</v>
       </c>
       <c r="BL10" t="s">
-        <v>286</v>
-      </c>
-      <c r="BM10" t="s">
+        <v>243</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>244</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ10" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT10" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU10" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" t="s">
-        <v>287</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS10" s="1">
-        <v>46068.311215277776</v>
-      </c>
-      <c r="BT10" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>64</v>
-      </c>
       <c r="BV10" t="s">
         <v>64</v>
       </c>
@@ -3687,36 +4421,51 @@
         <v>64</v>
       </c>
       <c r="BX10" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY10" t="s">
         <v>66</v>
       </c>
-      <c r="BY10" t="s">
+      <c r="BZ10" t="s">
         <v>70</v>
       </c>
-      <c r="BZ10">
+      <c r="CA10">
         <v>0</v>
       </c>
-      <c r="CD10">
+      <c r="CE10">
         <v>2</v>
       </c>
-      <c r="CF10" s="2">
-        <v>4096</v>
+      <c r="CG10" s="2">
+        <v>8192</v>
       </c>
       <c r="CJ10" t="s">
-        <v>281</v>
+        <v>204</v>
       </c>
       <c r="CK10" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL10" t="s">
-        <v>342</v>
+        <v>237</v>
+      </c>
+      <c r="CM10" t="s">
+        <v>383</v>
+      </c>
+      <c r="CN10" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO10" t="s">
+        <v>384</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>328</v>
       </c>
     </row>
-    <row r="11" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>330</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
@@ -3725,16 +4474,16 @@
         <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J11" t="s">
         <v>55</v>
@@ -3751,8 +4500,11 @@
       <c r="N11" t="s">
         <v>58</v>
       </c>
+      <c r="O11" t="s">
+        <v>331</v>
+      </c>
       <c r="P11" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="Q11" t="s">
         <v>59</v>
@@ -3770,13 +4522,13 @@
         <v>62</v>
       </c>
       <c r="V11" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="W11" t="s">
         <v>63</v>
       </c>
       <c r="X11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Y11" t="s">
         <v>64</v>
@@ -3788,64 +4540,88 @@
         <v>54</v>
       </c>
       <c r="AB11" s="1">
-        <v>46073.479155092595</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC11" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD11" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE11" t="s">
         <v>64</v>
       </c>
       <c r="AF11" t="s">
         <v>64</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>330</v>
       </c>
       <c r="AH11" t="s">
         <v>66</v>
       </c>
       <c r="AI11" t="s">
-        <v>189</v>
-      </c>
-      <c r="AJ11">
-        <v>9.6</v>
+        <v>286</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>86</v>
       </c>
       <c r="AK11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL11" t="s">
         <v>67</v>
       </c>
       <c r="AM11" t="s">
-        <v>68</v>
+        <v>78</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>79</v>
       </c>
       <c r="AP11">
         <v>1</v>
       </c>
       <c r="AQ11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR11" t="s">
         <v>70</v>
       </c>
       <c r="AS11">
-        <v>64</v>
+        <v>128</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>331</v>
       </c>
       <c r="AW11" t="s">
+        <v>285</v>
+      </c>
+      <c r="AX11" t="s">
         <v>288</v>
       </c>
-      <c r="AX11" t="s">
+      <c r="AY11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ11" s="2">
+        <v>8187</v>
+      </c>
+      <c r="BA11" t="s">
         <v>289</v>
       </c>
-      <c r="AZ11" s="2">
-        <v>3651</v>
-      </c>
-      <c r="BA11" t="s">
+      <c r="BC11" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD11" t="s">
         <v>290</v>
       </c>
-      <c r="BD11" t="s">
-        <v>86</v>
+      <c r="BE11" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>202</v>
       </c>
       <c r="BG11" t="s">
         <v>291</v>
@@ -3854,7 +4630,7 @@
         <v>292</v>
       </c>
       <c r="BJ11" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK11" t="b">
         <v>1</v>
@@ -3862,30 +4638,30 @@
       <c r="BL11" t="s">
         <v>293</v>
       </c>
-      <c r="BM11" t="s">
+      <c r="BN11" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>294</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ11" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT11" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU11" t="s">
         <v>83</v>
       </c>
-      <c r="BN11" t="s">
-        <v>294</v>
-      </c>
-      <c r="BO11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ11" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR11" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS11" s="1">
-        <v>46068.311215277776</v>
-      </c>
-      <c r="BT11" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU11" t="s">
-        <v>64</v>
-      </c>
       <c r="BV11" t="s">
         <v>64</v>
       </c>
@@ -3893,36 +4669,51 @@
         <v>64</v>
       </c>
       <c r="BX11" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY11" t="s">
         <v>66</v>
       </c>
-      <c r="BY11" t="s">
+      <c r="BZ11" t="s">
         <v>70</v>
       </c>
-      <c r="BZ11">
+      <c r="CA11">
         <v>0</v>
       </c>
-      <c r="CD11">
+      <c r="CE11">
         <v>2</v>
       </c>
-      <c r="CF11" s="2">
-        <v>4096</v>
+      <c r="CG11" s="2">
+        <v>8192</v>
       </c>
       <c r="CJ11" t="s">
-        <v>295</v>
+        <v>204</v>
       </c>
       <c r="CK11" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL11" t="s">
-        <v>342</v>
+        <v>287</v>
+      </c>
+      <c r="CM11" t="s">
+        <v>385</v>
+      </c>
+      <c r="CN11" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO11" t="s">
+        <v>386</v>
+      </c>
+      <c r="CP11" t="s">
+        <v>328</v>
       </c>
     </row>
-    <row r="12" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>277</v>
+        <v>194</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>179</v>
+      </c>
+      <c r="C12" t="s">
+        <v>336</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -3931,16 +4722,16 @@
         <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="I12" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="J12" t="s">
         <v>55</v>
@@ -3957,8 +4748,11 @@
       <c r="N12" t="s">
         <v>58</v>
       </c>
+      <c r="O12" t="s">
+        <v>331</v>
+      </c>
       <c r="P12" t="s">
-        <v>278</v>
+        <v>195</v>
       </c>
       <c r="Q12" t="s">
         <v>59</v>
@@ -3976,13 +4770,13 @@
         <v>62</v>
       </c>
       <c r="V12" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="W12" t="s">
         <v>63</v>
       </c>
       <c r="X12" t="s">
-        <v>296</v>
+        <v>208</v>
       </c>
       <c r="Y12" t="s">
         <v>64</v>
@@ -3994,112 +4788,136 @@
         <v>54</v>
       </c>
       <c r="AB12" s="1">
-        <v>46073.489861111113</v>
+        <v>46087.325694444444</v>
       </c>
       <c r="AC12" t="s">
         <v>65</v>
       </c>
       <c r="AD12" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE12" t="s">
         <v>64</v>
       </c>
       <c r="AF12" t="s">
         <v>64</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>336</v>
       </c>
       <c r="AH12" t="s">
         <v>66</v>
       </c>
       <c r="AI12" t="s">
-        <v>297</v>
+        <v>198</v>
       </c>
       <c r="AJ12" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="AK12" t="s">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AL12" t="s">
         <v>67</v>
       </c>
       <c r="AM12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AN12" t="s">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="AO12" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="AR12" t="s">
         <v>70</v>
       </c>
-      <c r="AS12">
-        <v>128</v>
+      <c r="AT12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>350</v>
       </c>
       <c r="AW12" t="s">
-        <v>296</v>
+        <v>208</v>
       </c>
       <c r="AX12" t="s">
-        <v>299</v>
+        <v>209</v>
       </c>
       <c r="AY12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AZ12" s="2">
-        <v>8187</v>
+        <v>8192</v>
       </c>
       <c r="BA12" t="s">
-        <v>300</v>
+        <v>210</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>202</v>
       </c>
       <c r="BD12" t="s">
-        <v>301</v>
+        <v>211</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>202</v>
       </c>
       <c r="BG12" t="s">
-        <v>302</v>
+        <v>212</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>387</v>
       </c>
       <c r="BI12" t="s">
-        <v>303</v>
+        <v>388</v>
       </c>
       <c r="BJ12" t="s">
-        <v>71</v>
+        <v>353</v>
       </c>
       <c r="BK12" t="b">
         <v>1</v>
       </c>
       <c r="BL12" t="s">
-        <v>304</v>
+        <v>213</v>
       </c>
       <c r="BM12" t="s">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="BN12" t="s">
-        <v>305</v>
+        <v>191</v>
       </c>
       <c r="BO12" t="s">
+        <v>214</v>
+      </c>
+      <c r="BP12" t="s">
         <v>64</v>
       </c>
       <c r="BQ12" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR12" t="s">
         <v>53</v>
       </c>
-      <c r="BR12" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS12" s="1">
-        <v>46072.268587962964</v>
-      </c>
-      <c r="BT12" t="s">
-        <v>84</v>
+      <c r="BS12" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT12" s="1">
+        <v>46088.834027777775</v>
       </c>
       <c r="BU12" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="BV12" t="s">
         <v>64</v>
@@ -4108,36 +4926,51 @@
         <v>64</v>
       </c>
       <c r="BX12" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY12" t="s">
         <v>66</v>
       </c>
-      <c r="BY12" t="s">
+      <c r="BZ12" t="s">
         <v>70</v>
       </c>
-      <c r="BZ12">
-        <v>0</v>
-      </c>
-      <c r="CD12">
+      <c r="CA12">
+        <v>280</v>
+      </c>
+      <c r="CB12">
         <v>2</v>
       </c>
-      <c r="CF12" s="2">
+      <c r="CE12">
+        <v>2</v>
+      </c>
+      <c r="CG12" s="2">
         <v>8192</v>
       </c>
       <c r="CJ12" t="s">
-        <v>298</v>
-      </c>
-      <c r="CK12" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="CL12" t="s">
-        <v>342</v>
+        <v>355</v>
+      </c>
+      <c r="CN12" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO12" t="s">
+        <v>390</v>
+      </c>
+      <c r="CP12" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="13" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>306</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>179</v>
+      </c>
+      <c r="C13" t="s">
+        <v>336</v>
       </c>
       <c r="D13" t="s">
         <v>53</v>
@@ -4146,16 +4979,16 @@
         <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G13" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H13" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I13" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J13" t="s">
         <v>55</v>
@@ -4164,7 +4997,7 @@
         <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="M13" t="s">
         <v>58</v>
@@ -4172,8 +5005,11 @@
       <c r="N13" t="s">
         <v>58</v>
       </c>
+      <c r="O13" t="s">
+        <v>331</v>
+      </c>
       <c r="P13" t="s">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="Q13" t="s">
         <v>59</v>
@@ -4191,13 +5027,13 @@
         <v>62</v>
       </c>
       <c r="V13" t="s">
-        <v>308</v>
+        <v>196</v>
       </c>
       <c r="W13" t="s">
         <v>63</v>
       </c>
       <c r="X13" t="s">
-        <v>309</v>
+        <v>391</v>
       </c>
       <c r="Y13" t="s">
         <v>64</v>
@@ -4209,113 +5045,125 @@
         <v>54</v>
       </c>
       <c r="AB13" s="1">
-        <v>46073.489861111113</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC13" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD13" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE13" t="s">
         <v>64</v>
       </c>
       <c r="AF13" t="s">
         <v>64</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>336</v>
       </c>
       <c r="AH13" t="s">
         <v>66</v>
       </c>
       <c r="AI13" t="s">
-        <v>237</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>206</v>
+        <v>392</v>
+      </c>
+      <c r="AJ13">
+        <v>9.5</v>
       </c>
       <c r="AK13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL13" t="s">
         <v>67</v>
       </c>
       <c r="AM13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>393</v>
+      </c>
+      <c r="AO13" t="s">
         <v>79</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>80</v>
       </c>
       <c r="AP13">
         <v>1</v>
       </c>
       <c r="AQ13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR13" t="s">
         <v>70</v>
       </c>
       <c r="AS13">
-        <v>128</v>
+        <v>64</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>331</v>
       </c>
       <c r="AW13" t="s">
-        <v>309</v>
+        <v>391</v>
       </c>
       <c r="AX13" t="s">
-        <v>311</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="AZ13" s="2">
-        <v>8191</v>
+        <v>3455</v>
       </c>
       <c r="BA13" t="s">
-        <v>312</v>
+        <v>395</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>202</v>
       </c>
       <c r="BD13" t="s">
-        <v>301</v>
+        <v>342</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>202</v>
       </c>
       <c r="BG13" t="s">
-        <v>313</v>
+        <v>396</v>
       </c>
       <c r="BI13" t="s">
-        <v>314</v>
+        <v>397</v>
       </c>
       <c r="BJ13" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK13" t="b">
         <v>1</v>
       </c>
       <c r="BL13" t="s">
-        <v>315</v>
-      </c>
-      <c r="BM13" t="s">
+        <v>398</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO13" t="s">
+        <v>399</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ13" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS13" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT13" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU13" t="s">
         <v>83</v>
       </c>
-      <c r="BN13" t="s">
-        <v>316</v>
-      </c>
-      <c r="BO13" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ13" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR13" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS13" s="1">
-        <v>46068.311215277776</v>
-      </c>
-      <c r="BT13" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU13" t="s">
-        <v>64</v>
-      </c>
       <c r="BV13" t="s">
         <v>64</v>
       </c>
@@ -4323,36 +5171,51 @@
         <v>64</v>
       </c>
       <c r="BX13" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY13" t="s">
         <v>66</v>
       </c>
-      <c r="BY13" t="s">
+      <c r="BZ13" t="s">
         <v>70</v>
       </c>
-      <c r="BZ13">
+      <c r="CA13">
         <v>0</v>
       </c>
-      <c r="CD13">
+      <c r="CE13">
         <v>2</v>
       </c>
-      <c r="CF13" s="2">
-        <v>8192</v>
+      <c r="CG13" s="2">
+        <v>4096</v>
       </c>
       <c r="CJ13" t="s">
-        <v>310</v>
+        <v>204</v>
       </c>
       <c r="CK13" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL13" t="s">
-        <v>340</v>
+        <v>393</v>
+      </c>
+      <c r="CM13" t="s">
+        <v>400</v>
+      </c>
+      <c r="CN13" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO13" t="s">
+        <v>401</v>
+      </c>
+      <c r="CP13" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="14" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>179</v>
+      </c>
+      <c r="C14" t="s">
+        <v>330</v>
       </c>
       <c r="D14" t="s">
         <v>53</v>
@@ -4361,16 +5224,16 @@
         <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="I14" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="J14" t="s">
         <v>55</v>
@@ -4387,8 +5250,11 @@
       <c r="N14" t="s">
         <v>58</v>
       </c>
+      <c r="O14" t="s">
+        <v>331</v>
+      </c>
       <c r="P14" t="s">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="Q14" t="s">
         <v>59</v>
@@ -4406,13 +5272,13 @@
         <v>62</v>
       </c>
       <c r="V14" t="s">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="W14" t="s">
         <v>63</v>
       </c>
       <c r="X14" t="s">
-        <v>92</v>
+        <v>311</v>
       </c>
       <c r="Y14" t="s">
         <v>64</v>
@@ -4424,31 +5290,34 @@
         <v>54</v>
       </c>
       <c r="AB14" s="1">
-        <v>46073.492268518516</v>
+        <v>46089.23333333333</v>
       </c>
       <c r="AC14" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD14" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE14" t="s">
         <v>64</v>
       </c>
       <c r="AF14" t="s">
         <v>64</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>330</v>
       </c>
       <c r="AH14" t="s">
         <v>66</v>
       </c>
       <c r="AI14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ14">
         <v>24.04</v>
       </c>
       <c r="AK14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL14" t="s">
         <v>67</v>
@@ -4457,77 +5326,89 @@
         <v>68</v>
       </c>
       <c r="AN14" t="s">
-        <v>94</v>
+        <v>312</v>
       </c>
       <c r="AO14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AP14">
         <v>1</v>
       </c>
       <c r="AQ14" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="AR14" t="s">
         <v>70</v>
       </c>
       <c r="AS14">
-        <v>54</v>
+        <v>256</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>331</v>
       </c>
       <c r="AW14" t="s">
-        <v>92</v>
+        <v>311</v>
       </c>
       <c r="AX14" t="s">
-        <v>95</v>
+        <v>313</v>
       </c>
       <c r="AZ14" s="2">
-        <v>3913</v>
+        <v>7944</v>
       </c>
       <c r="BA14" t="s">
-        <v>96</v>
+        <v>314</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>202</v>
       </c>
       <c r="BD14" t="s">
-        <v>86</v>
+        <v>315</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>202</v>
       </c>
       <c r="BG14" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="BI14" t="s">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="BJ14" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK14" t="b">
         <v>1</v>
       </c>
       <c r="BL14" t="s">
-        <v>99</v>
-      </c>
-      <c r="BM14" t="s">
+        <v>318</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO14" t="s">
+        <v>311</v>
+      </c>
+      <c r="BP14" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ14" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR14" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS14" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT14" s="1">
+        <v>46089.313194444447</v>
+      </c>
+      <c r="BU14" t="s">
         <v>83</v>
       </c>
-      <c r="BN14" t="s">
-        <v>100</v>
-      </c>
-      <c r="BO14" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ14" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR14" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS14" s="1">
-        <v>46072.268599537034</v>
-      </c>
-      <c r="BT14" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU14" t="s">
-        <v>64</v>
-      </c>
       <c r="BV14" t="s">
         <v>64</v>
       </c>
@@ -4535,36 +5416,51 @@
         <v>64</v>
       </c>
       <c r="BX14" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY14" t="s">
         <v>66</v>
       </c>
-      <c r="BY14" t="s">
+      <c r="BZ14" t="s">
         <v>70</v>
       </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
-      <c r="CD14">
+      <c r="CA14">
+        <v>16</v>
+      </c>
+      <c r="CE14">
         <v>2</v>
       </c>
-      <c r="CF14" s="2">
-        <v>4096</v>
+      <c r="CG14" s="2">
+        <v>8192</v>
       </c>
       <c r="CJ14" t="s">
-        <v>94</v>
+        <v>204</v>
       </c>
       <c r="CK14" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL14" t="s">
-        <v>341</v>
+        <v>312</v>
+      </c>
+      <c r="CM14" t="s">
+        <v>402</v>
+      </c>
+      <c r="CN14" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO14" t="s">
+        <v>403</v>
+      </c>
+      <c r="CP14" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="15" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>330</v>
       </c>
       <c r="D15" t="s">
         <v>53</v>
@@ -4573,16 +5469,16 @@
         <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J15" t="s">
         <v>55</v>
@@ -4599,8 +5495,11 @@
       <c r="N15" t="s">
         <v>58</v>
       </c>
+      <c r="O15" t="s">
+        <v>331</v>
+      </c>
       <c r="P15" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="Q15" t="s">
         <v>59</v>
@@ -4618,13 +5517,13 @@
         <v>62</v>
       </c>
       <c r="V15" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="W15" t="s">
         <v>63</v>
       </c>
       <c r="X15" t="s">
-        <v>101</v>
+        <v>404</v>
       </c>
       <c r="Y15" t="s">
         <v>64</v>
@@ -4636,10 +5535,10 @@
         <v>54</v>
       </c>
       <c r="AB15" s="1">
-        <v>46073.492951388886</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC15" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD15" t="s">
         <v>64</v>
@@ -4649,18 +5548,21 @@
       </c>
       <c r="AF15" t="s">
         <v>64</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>330</v>
       </c>
       <c r="AH15" t="s">
         <v>66</v>
       </c>
       <c r="AI15" t="s">
-        <v>102</v>
+        <v>368</v>
       </c>
       <c r="AJ15">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="AK15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL15" t="s">
         <v>67</v>
@@ -4669,77 +5571,92 @@
         <v>68</v>
       </c>
       <c r="AN15" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="AO15" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AP15">
         <v>1</v>
       </c>
       <c r="AQ15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AR15" t="s">
         <v>70</v>
       </c>
       <c r="AS15">
-        <v>256</v>
+        <v>64</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>331</v>
       </c>
       <c r="AW15" t="s">
-        <v>101</v>
+        <v>404</v>
       </c>
       <c r="AX15" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="AZ15" s="2">
-        <v>7698</v>
+        <v>3785</v>
       </c>
       <c r="BA15" t="s">
-        <v>105</v>
+        <v>405</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>202</v>
       </c>
       <c r="BD15" t="s">
-        <v>106</v>
+        <v>370</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>202</v>
       </c>
       <c r="BG15" t="s">
-        <v>107</v>
+        <v>170</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>363</v>
       </c>
       <c r="BI15" t="s">
-        <v>108</v>
+        <v>406</v>
       </c>
       <c r="BJ15" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK15" t="b">
         <v>1</v>
       </c>
       <c r="BL15" t="s">
-        <v>109</v>
-      </c>
-      <c r="BM15" t="s">
+        <v>171</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO15" t="s">
+        <v>167</v>
+      </c>
+      <c r="BP15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ15" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR15" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS15" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT15" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU15" t="s">
         <v>83</v>
       </c>
-      <c r="BN15" t="s">
-        <v>101</v>
-      </c>
-      <c r="BO15" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ15" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR15" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS15" s="1">
-        <v>46072.841134259259</v>
-      </c>
-      <c r="BT15" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU15" t="s">
-        <v>64</v>
-      </c>
       <c r="BV15" t="s">
         <v>64</v>
       </c>
@@ -4747,36 +5664,51 @@
         <v>64</v>
       </c>
       <c r="BX15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY15" t="s">
         <v>66</v>
       </c>
-      <c r="BY15" t="s">
+      <c r="BZ15" t="s">
         <v>70</v>
       </c>
-      <c r="BZ15">
-        <v>16</v>
-      </c>
-      <c r="CD15">
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CE15">
         <v>2</v>
       </c>
-      <c r="CF15" s="2">
-        <v>8192</v>
+      <c r="CG15" s="2">
+        <v>4096</v>
       </c>
       <c r="CJ15" t="s">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="CK15" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL15" t="s">
-        <v>341</v>
+        <v>169</v>
+      </c>
+      <c r="CM15" t="s">
+        <v>407</v>
+      </c>
+      <c r="CN15" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO15" t="s">
+        <v>408</v>
+      </c>
+      <c r="CP15" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="16" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>330</v>
       </c>
       <c r="D16" t="s">
         <v>53</v>
@@ -4785,16 +5717,16 @@
         <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J16" t="s">
         <v>55</v>
@@ -4811,8 +5743,11 @@
       <c r="N16" t="s">
         <v>58</v>
       </c>
+      <c r="O16" t="s">
+        <v>331</v>
+      </c>
       <c r="P16" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="Q16" t="s">
         <v>59</v>
@@ -4830,13 +5765,13 @@
         <v>62</v>
       </c>
       <c r="V16" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="W16" t="s">
         <v>63</v>
       </c>
       <c r="X16" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="Y16" t="s">
         <v>64</v>
@@ -4848,113 +5783,125 @@
         <v>54</v>
       </c>
       <c r="AB16" s="1">
-        <v>46073.490682870368</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC16" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD16" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE16" t="s">
         <v>64</v>
       </c>
       <c r="AF16" t="s">
         <v>64</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>330</v>
       </c>
       <c r="AH16" t="s">
         <v>66</v>
       </c>
       <c r="AI16" t="s">
-        <v>111</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>112</v>
+        <v>100</v>
+      </c>
+      <c r="AJ16">
+        <v>8.1</v>
       </c>
       <c r="AK16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s">
         <v>67</v>
       </c>
       <c r="AM16" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO16" t="s">
         <v>79</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>113</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>85</v>
       </c>
       <c r="AP16">
         <v>1</v>
       </c>
       <c r="AQ16" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AR16" t="s">
         <v>70</v>
       </c>
       <c r="AS16">
-        <v>256</v>
+        <v>64</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>331</v>
       </c>
       <c r="AW16" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="AX16" t="s">
-        <v>114</v>
-      </c>
-      <c r="AY16" t="s">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AZ16" s="2">
-        <v>8192</v>
+        <v>3661</v>
       </c>
       <c r="BA16" t="s">
-        <v>115</v>
+        <v>162</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>202</v>
       </c>
       <c r="BD16" t="s">
-        <v>116</v>
+        <v>85</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>202</v>
       </c>
       <c r="BG16" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="BI16" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="BJ16" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK16" t="b">
         <v>1</v>
       </c>
       <c r="BL16" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM16" t="s">
+        <v>165</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO16" t="s">
+        <v>166</v>
+      </c>
+      <c r="BP16" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ16" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR16" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS16" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT16" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU16" t="s">
         <v>83</v>
       </c>
-      <c r="BN16" t="s">
-        <v>110</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ16" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR16" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS16" s="1">
-        <v>46070.841261574074</v>
-      </c>
-      <c r="BT16" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU16" t="s">
-        <v>64</v>
-      </c>
       <c r="BV16" t="s">
         <v>64</v>
       </c>
@@ -4962,36 +5909,51 @@
         <v>64</v>
       </c>
       <c r="BX16" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY16" t="s">
         <v>66</v>
       </c>
-      <c r="BY16" t="s">
+      <c r="BZ16" t="s">
         <v>70</v>
       </c>
-      <c r="BZ16">
-        <v>16</v>
-      </c>
-      <c r="CD16">
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CE16">
         <v>2</v>
       </c>
-      <c r="CF16" s="2">
-        <v>8192</v>
+      <c r="CG16" s="2">
+        <v>4096</v>
       </c>
       <c r="CJ16" t="s">
-        <v>113</v>
+        <v>204</v>
       </c>
       <c r="CK16" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL16" t="s">
-        <v>341</v>
+        <v>160</v>
+      </c>
+      <c r="CM16" t="s">
+        <v>409</v>
+      </c>
+      <c r="CN16" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO16" t="s">
+        <v>410</v>
+      </c>
+      <c r="CP16" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="17" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>336</v>
       </c>
       <c r="D17" t="s">
         <v>53</v>
@@ -5000,16 +5962,16 @@
         <v>54</v>
       </c>
       <c r="F17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -5026,8 +5988,11 @@
       <c r="N17" t="s">
         <v>58</v>
       </c>
+      <c r="O17" t="s">
+        <v>331</v>
+      </c>
       <c r="P17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q17" t="s">
         <v>59</v>
@@ -5045,13 +6010,13 @@
         <v>62</v>
       </c>
       <c r="V17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W17" t="s">
         <v>63</v>
       </c>
       <c r="X17" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="Y17" t="s">
         <v>64</v>
@@ -5063,10 +6028,10 @@
         <v>54</v>
       </c>
       <c r="AB17" s="1">
-        <v>46072.839097222219</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD17" t="s">
         <v>64</v>
@@ -5076,15 +6041,21 @@
       </c>
       <c r="AF17" t="s">
         <v>64</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>336</v>
       </c>
       <c r="AH17" t="s">
         <v>66</v>
       </c>
       <c r="AI17" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="AJ17">
-        <v>6.1</v>
+        <v>24.04</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>77</v>
       </c>
       <c r="AL17" t="s">
         <v>67</v>
@@ -5092,63 +6063,93 @@
       <c r="AM17" t="s">
         <v>68</v>
       </c>
+      <c r="AN17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>79</v>
+      </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>80</v>
       </c>
       <c r="AR17" t="s">
         <v>70</v>
       </c>
       <c r="AS17">
-        <v>64</v>
+        <v>54</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>331</v>
       </c>
       <c r="AW17" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="AX17" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="AZ17" s="2">
-        <v>4096</v>
+        <v>3913</v>
       </c>
       <c r="BA17" t="s">
-        <v>123</v>
+        <v>95</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>85</v>
+      </c>
+      <c r="BE17" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>202</v>
       </c>
       <c r="BG17" t="s">
-        <v>124</v>
+        <v>96</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>363</v>
+      </c>
+      <c r="BI17" t="s">
+        <v>411</v>
       </c>
       <c r="BJ17" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK17" t="b">
         <v>1</v>
       </c>
       <c r="BL17" t="s">
-        <v>125</v>
-      </c>
-      <c r="BM17" t="s">
+        <v>97</v>
+      </c>
+      <c r="BN17" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO17" t="s">
+        <v>98</v>
+      </c>
+      <c r="BP17" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ17" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR17" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS17" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT17" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU17" t="s">
         <v>83</v>
       </c>
-      <c r="BN17" t="s">
-        <v>120</v>
-      </c>
-      <c r="BO17" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ17" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR17" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS17" s="1">
-        <v>46072.839097222219</v>
-      </c>
-      <c r="BT17" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU17" t="s">
-        <v>64</v>
-      </c>
       <c r="BV17" t="s">
         <v>64</v>
       </c>
@@ -5156,36 +6157,51 @@
         <v>64</v>
       </c>
       <c r="BX17" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY17" t="s">
         <v>66</v>
       </c>
-      <c r="BY17" t="s">
+      <c r="BZ17" t="s">
         <v>70</v>
       </c>
-      <c r="BZ17">
+      <c r="CA17">
         <v>0</v>
       </c>
-      <c r="CD17">
+      <c r="CE17">
         <v>2</v>
       </c>
-      <c r="CF17" s="2">
+      <c r="CG17" s="2">
         <v>4096</v>
       </c>
       <c r="CJ17" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="CK17" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL17" t="s">
-        <v>341</v>
+        <v>93</v>
+      </c>
+      <c r="CM17" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN17" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO17" t="s">
+        <v>413</v>
+      </c>
+      <c r="CP17" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="18" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>122</v>
       </c>
       <c r="B18" t="s">
-        <v>184</v>
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>362</v>
       </c>
       <c r="D18" t="s">
         <v>53</v>
@@ -5194,16 +6210,16 @@
         <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>185</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="J18" t="s">
         <v>55</v>
@@ -5212,7 +6228,7 @@
         <v>56</v>
       </c>
       <c r="L18" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="M18" t="s">
         <v>58</v>
@@ -5220,8 +6236,11 @@
       <c r="N18" t="s">
         <v>58</v>
       </c>
+      <c r="O18" t="s">
+        <v>331</v>
+      </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>123</v>
       </c>
       <c r="Q18" t="s">
         <v>59</v>
@@ -5239,13 +6258,13 @@
         <v>62</v>
       </c>
       <c r="V18" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="W18" t="s">
         <v>63</v>
       </c>
       <c r="X18" t="s">
-        <v>317</v>
+        <v>140</v>
       </c>
       <c r="Y18" t="s">
         <v>64</v>
@@ -5257,28 +6276,34 @@
         <v>54</v>
       </c>
       <c r="AB18" s="1">
-        <v>46072.839108796295</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD18" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE18" t="s">
         <v>64</v>
       </c>
       <c r="AF18" t="s">
         <v>64</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>362</v>
       </c>
       <c r="AH18" t="s">
         <v>66</v>
       </c>
       <c r="AI18" t="s">
-        <v>318</v>
+        <v>100</v>
       </c>
       <c r="AJ18">
-        <v>20.04</v>
+        <v>8.1</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>77</v>
       </c>
       <c r="AL18" t="s">
         <v>67</v>
@@ -5287,62 +6312,89 @@
         <v>68</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>80</v>
       </c>
       <c r="AR18" t="s">
         <v>70</v>
       </c>
       <c r="AS18">
-        <v>54</v>
+        <v>64</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>58</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>331</v>
       </c>
       <c r="AW18" t="s">
-        <v>317</v>
+        <v>140</v>
       </c>
       <c r="AX18" t="s">
-        <v>319</v>
+        <v>141</v>
       </c>
       <c r="AZ18" s="2">
-        <v>4096</v>
+        <v>3661</v>
       </c>
       <c r="BA18" t="s">
-        <v>320</v>
+        <v>142</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>414</v>
+      </c>
+      <c r="BE18" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>202</v>
       </c>
       <c r="BG18" t="s">
-        <v>321</v>
+        <v>143</v>
+      </c>
+      <c r="BI18" t="s">
+        <v>144</v>
       </c>
       <c r="BJ18" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK18" t="b">
         <v>1</v>
       </c>
       <c r="BL18" t="s">
-        <v>322</v>
-      </c>
-      <c r="BM18" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN18" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO18" t="s">
+        <v>146</v>
+      </c>
+      <c r="BP18" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ18" t="s">
+        <v>362</v>
+      </c>
+      <c r="BR18" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS18" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT18" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU18" t="s">
         <v>83</v>
       </c>
-      <c r="BN18" t="s">
-        <v>317</v>
-      </c>
-      <c r="BO18" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ18" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR18" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS18" s="1">
-        <v>46072.839108796295</v>
-      </c>
-      <c r="BT18" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU18" t="s">
-        <v>64</v>
-      </c>
       <c r="BV18" t="s">
         <v>64</v>
       </c>
@@ -5350,36 +6402,57 @@
         <v>64</v>
       </c>
       <c r="BX18" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY18" t="s">
         <v>66</v>
       </c>
-      <c r="BY18" t="s">
+      <c r="BZ18" t="s">
         <v>70</v>
       </c>
-      <c r="BZ18">
+      <c r="CA18">
         <v>0</v>
       </c>
-      <c r="CD18">
+      <c r="CC18" t="s">
+        <v>58</v>
+      </c>
+      <c r="CD18" t="s">
+        <v>58</v>
+      </c>
+      <c r="CE18">
         <v>2</v>
       </c>
-      <c r="CF18" s="2">
+      <c r="CG18" s="2">
         <v>4096</v>
       </c>
       <c r="CJ18" t="s">
-        <v>320</v>
+        <v>204</v>
       </c>
       <c r="CK18" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL18" t="s">
-        <v>340</v>
+        <v>147</v>
+      </c>
+      <c r="CM18" t="s">
+        <v>415</v>
+      </c>
+      <c r="CN18" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO18" t="s">
+        <v>416</v>
+      </c>
+      <c r="CP18" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="19" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>362</v>
       </c>
       <c r="D19" t="s">
         <v>53</v>
@@ -5388,16 +6461,16 @@
         <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J19" t="s">
         <v>55</v>
@@ -5414,8 +6487,11 @@
       <c r="N19" t="s">
         <v>58</v>
       </c>
+      <c r="O19" t="s">
+        <v>331</v>
+      </c>
       <c r="P19" t="s">
-        <v>127</v>
+        <v>254</v>
       </c>
       <c r="Q19" t="s">
         <v>59</v>
@@ -5433,13 +6509,13 @@
         <v>62</v>
       </c>
       <c r="V19" t="s">
-        <v>128</v>
+        <v>255</v>
       </c>
       <c r="W19" t="s">
         <v>63</v>
       </c>
       <c r="X19" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="Y19" t="s">
         <v>64</v>
@@ -5451,98 +6527,128 @@
         <v>54</v>
       </c>
       <c r="AB19" s="1">
-        <v>46072.839131944442</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD19" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE19" t="s">
         <v>64</v>
       </c>
       <c r="AF19" t="s">
         <v>64</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>362</v>
       </c>
       <c r="AH19" t="s">
         <v>66</v>
       </c>
       <c r="AI19" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ19">
-        <v>15.2</v>
+        <v>257</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>258</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>77</v>
       </c>
       <c r="AL19" t="s">
         <v>67</v>
       </c>
       <c r="AM19" t="s">
-        <v>68</v>
+        <v>78</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>259</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>79</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>80</v>
       </c>
       <c r="AR19" t="s">
         <v>70</v>
       </c>
       <c r="AS19">
-        <v>30</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU19" t="s">
-        <v>58</v>
+        <v>128</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>331</v>
       </c>
       <c r="AW19" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="AX19" t="s">
-        <v>131</v>
+        <v>260</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>81</v>
       </c>
       <c r="AZ19" s="2">
-        <v>4096</v>
-      </c>
-      <c r="BA19" s="3" t="s">
-        <v>132</v>
+        <v>8187</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>261</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>417</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF19" t="s">
+        <v>202</v>
       </c>
       <c r="BG19" t="s">
-        <v>133</v>
+        <v>262</v>
+      </c>
+      <c r="BI19" t="s">
+        <v>263</v>
       </c>
       <c r="BJ19" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK19" t="b">
         <v>1</v>
       </c>
       <c r="BL19" t="s">
-        <v>134</v>
-      </c>
-      <c r="BM19" t="s">
+        <v>264</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO19" t="s">
+        <v>265</v>
+      </c>
+      <c r="BP19" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ19" t="s">
+        <v>362</v>
+      </c>
+      <c r="BR19" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS19" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT19" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU19" t="s">
         <v>83</v>
       </c>
-      <c r="BN19" t="s">
-        <v>129</v>
-      </c>
-      <c r="BO19" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ19" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR19" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS19" s="1">
-        <v>46072.839120370372</v>
-      </c>
-      <c r="BT19" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU19" t="s">
-        <v>64</v>
-      </c>
       <c r="BV19" t="s">
         <v>64</v>
       </c>
@@ -5550,42 +6656,51 @@
         <v>64</v>
       </c>
       <c r="BX19" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY19" t="s">
         <v>66</v>
       </c>
-      <c r="BY19" t="s">
+      <c r="BZ19" t="s">
         <v>70</v>
       </c>
-      <c r="BZ19">
+      <c r="CA19">
         <v>0</v>
       </c>
-      <c r="CB19" t="s">
-        <v>58</v>
-      </c>
-      <c r="CC19" t="s">
-        <v>58</v>
-      </c>
-      <c r="CD19">
+      <c r="CE19">
         <v>2</v>
       </c>
-      <c r="CF19" s="2">
-        <v>4096</v>
-      </c>
-      <c r="CJ19" s="3" t="s">
-        <v>132</v>
+      <c r="CG19" s="2">
+        <v>8192</v>
+      </c>
+      <c r="CJ19" t="s">
+        <v>204</v>
       </c>
       <c r="CK19" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL19" t="s">
-        <v>341</v>
+        <v>259</v>
+      </c>
+      <c r="CM19" t="s">
+        <v>418</v>
+      </c>
+      <c r="CN19" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO19" t="s">
+        <v>419</v>
+      </c>
+      <c r="CP19" t="s">
+        <v>328</v>
       </c>
     </row>
-    <row r="20" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>336</v>
       </c>
       <c r="D20" t="s">
         <v>53</v>
@@ -5594,16 +6709,16 @@
         <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J20" t="s">
         <v>55</v>
@@ -5612,7 +6727,7 @@
         <v>56</v>
       </c>
       <c r="L20" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="M20" t="s">
         <v>58</v>
@@ -5620,8 +6735,11 @@
       <c r="N20" t="s">
         <v>58</v>
       </c>
+      <c r="O20" t="s">
+        <v>331</v>
+      </c>
       <c r="P20" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="Q20" t="s">
         <v>59</v>
@@ -5639,13 +6757,13 @@
         <v>62</v>
       </c>
       <c r="V20" t="s">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="W20" t="s">
         <v>63</v>
       </c>
       <c r="X20" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="Y20" t="s">
         <v>64</v>
@@ -5657,116 +6775,128 @@
         <v>54</v>
       </c>
       <c r="AB20" s="1">
-        <v>46073.471990740742</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC20" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD20" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE20" t="s">
         <v>64</v>
       </c>
       <c r="AF20" t="s">
         <v>64</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>336</v>
       </c>
       <c r="AH20" t="s">
         <v>66</v>
       </c>
       <c r="AI20" t="s">
-        <v>136</v>
-      </c>
-      <c r="AJ20">
-        <v>15.6</v>
+        <v>227</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>199</v>
       </c>
       <c r="AK20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s">
         <v>67</v>
       </c>
       <c r="AM20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="AN20" t="s">
-        <v>137</v>
+        <v>228</v>
       </c>
       <c r="AO20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP20">
         <v>1</v>
       </c>
       <c r="AQ20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR20" t="s">
         <v>70</v>
       </c>
       <c r="AS20">
-        <v>30</v>
-      </c>
-      <c r="AT20" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU20" t="s">
-        <v>58</v>
+        <v>128</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>331</v>
       </c>
       <c r="AW20" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="AX20" t="s">
-        <v>138</v>
+        <v>229</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>81</v>
       </c>
       <c r="AZ20" s="2">
-        <v>3624</v>
+        <v>8191</v>
       </c>
       <c r="BA20" t="s">
-        <v>139</v>
+        <v>230</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>202</v>
       </c>
       <c r="BD20" t="s">
-        <v>140</v>
+        <v>231</v>
+      </c>
+      <c r="BE20" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>202</v>
       </c>
       <c r="BG20" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="BI20" t="s">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="BJ20" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK20" t="b">
         <v>1</v>
       </c>
       <c r="BL20" t="s">
-        <v>143</v>
-      </c>
-      <c r="BM20" t="s">
+        <v>234</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO20" t="s">
+        <v>235</v>
+      </c>
+      <c r="BP20" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ20" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR20" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS20" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT20" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU20" t="s">
         <v>83</v>
       </c>
-      <c r="BN20" t="s">
-        <v>144</v>
-      </c>
-      <c r="BO20" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ20" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR20" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS20" s="1">
-        <v>46072.268576388888</v>
-      </c>
-      <c r="BT20" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU20" t="s">
-        <v>64</v>
-      </c>
       <c r="BV20" t="s">
         <v>64</v>
       </c>
@@ -5774,42 +6904,51 @@
         <v>64</v>
       </c>
       <c r="BX20" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY20" t="s">
         <v>66</v>
       </c>
-      <c r="BY20" t="s">
+      <c r="BZ20" t="s">
         <v>70</v>
       </c>
-      <c r="BZ20">
+      <c r="CA20">
         <v>0</v>
       </c>
-      <c r="CB20" t="s">
-        <v>58</v>
-      </c>
-      <c r="CC20" t="s">
-        <v>58</v>
-      </c>
-      <c r="CD20">
+      <c r="CE20">
         <v>2</v>
       </c>
-      <c r="CF20" s="2">
-        <v>4096</v>
+      <c r="CG20" s="2">
+        <v>8192</v>
       </c>
       <c r="CJ20" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="CK20" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL20" t="s">
-        <v>341</v>
+        <v>228</v>
+      </c>
+      <c r="CM20" t="s">
+        <v>420</v>
+      </c>
+      <c r="CN20" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO20" t="s">
+        <v>421</v>
+      </c>
+      <c r="CP20" t="s">
+        <v>328</v>
       </c>
     </row>
-    <row r="21" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>266</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>330</v>
       </c>
       <c r="D21" t="s">
         <v>53</v>
@@ -5818,16 +6957,16 @@
         <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J21" t="s">
         <v>55</v>
@@ -5836,7 +6975,7 @@
         <v>56</v>
       </c>
       <c r="L21" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="M21" t="s">
         <v>58</v>
@@ -5844,8 +6983,11 @@
       <c r="N21" t="s">
         <v>58</v>
       </c>
+      <c r="O21" t="s">
+        <v>331</v>
+      </c>
       <c r="P21" t="s">
-        <v>127</v>
+        <v>267</v>
       </c>
       <c r="Q21" t="s">
         <v>59</v>
@@ -5863,13 +7005,13 @@
         <v>62</v>
       </c>
       <c r="V21" t="s">
-        <v>128</v>
+        <v>268</v>
       </c>
       <c r="W21" t="s">
         <v>63</v>
       </c>
       <c r="X21" t="s">
-        <v>145</v>
+        <v>277</v>
       </c>
       <c r="Y21" t="s">
         <v>64</v>
@@ -5881,31 +7023,34 @@
         <v>54</v>
       </c>
       <c r="AB21" s="1">
-        <v>46073.489861111113</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC21" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD21" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE21" t="s">
         <v>64</v>
       </c>
       <c r="AF21" t="s">
         <v>64</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>330</v>
       </c>
       <c r="AH21" t="s">
         <v>66</v>
       </c>
       <c r="AI21" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="AJ21">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="AK21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL21" t="s">
         <v>67</v>
@@ -5917,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="AQ21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR21" t="s">
         <v>70</v>
@@ -5925,66 +7070,72 @@
       <c r="AS21">
         <v>64</v>
       </c>
-      <c r="AT21" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU21" t="s">
-        <v>58</v>
+      <c r="AV21" t="s">
+        <v>331</v>
       </c>
       <c r="AW21" t="s">
-        <v>145</v>
+        <v>277</v>
       </c>
       <c r="AX21" t="s">
-        <v>146</v>
+        <v>278</v>
       </c>
       <c r="AZ21" s="2">
-        <v>3661</v>
+        <v>3651</v>
       </c>
       <c r="BA21" t="s">
-        <v>147</v>
+        <v>279</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>202</v>
       </c>
       <c r="BD21" t="s">
-        <v>86</v>
+        <v>414</v>
+      </c>
+      <c r="BE21" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>202</v>
       </c>
       <c r="BG21" t="s">
-        <v>148</v>
+        <v>280</v>
       </c>
       <c r="BI21" t="s">
-        <v>149</v>
+        <v>281</v>
       </c>
       <c r="BJ21" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK21" t="b">
         <v>1</v>
       </c>
       <c r="BL21" t="s">
-        <v>150</v>
-      </c>
-      <c r="BM21" t="s">
+        <v>282</v>
+      </c>
+      <c r="BN21" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO21" t="s">
+        <v>283</v>
+      </c>
+      <c r="BP21" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ21" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR21" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS21" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT21" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU21" t="s">
         <v>83</v>
       </c>
-      <c r="BN21" t="s">
-        <v>151</v>
-      </c>
-      <c r="BO21" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ21" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR21" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS21" s="1">
-        <v>46068.311215277776</v>
-      </c>
-      <c r="BT21" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU21" t="s">
-        <v>64</v>
-      </c>
       <c r="BV21" t="s">
         <v>64</v>
       </c>
@@ -5992,42 +7143,51 @@
         <v>64</v>
       </c>
       <c r="BX21" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY21" t="s">
         <v>66</v>
       </c>
-      <c r="BY21" t="s">
+      <c r="BZ21" t="s">
         <v>70</v>
       </c>
-      <c r="BZ21">
+      <c r="CA21">
         <v>0</v>
       </c>
-      <c r="CB21" t="s">
-        <v>58</v>
-      </c>
-      <c r="CC21" t="s">
-        <v>58</v>
-      </c>
-      <c r="CD21">
+      <c r="CE21">
         <v>2</v>
       </c>
-      <c r="CF21" s="2">
+      <c r="CG21" s="2">
         <v>4096</v>
       </c>
       <c r="CJ21" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="CK21" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL21" t="s">
-        <v>341</v>
+        <v>284</v>
+      </c>
+      <c r="CM21" t="s">
+        <v>422</v>
+      </c>
+      <c r="CN21" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO21" t="s">
+        <v>423</v>
+      </c>
+      <c r="CP21" t="s">
+        <v>328</v>
       </c>
     </row>
-    <row r="22" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>179</v>
+      </c>
+      <c r="C22" t="s">
+        <v>336</v>
       </c>
       <c r="D22" t="s">
         <v>53</v>
@@ -6036,16 +7196,16 @@
         <v>54</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="H22" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="I22" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="J22" t="s">
         <v>55</v>
@@ -6062,8 +7222,11 @@
       <c r="N22" t="s">
         <v>58</v>
       </c>
+      <c r="O22" t="s">
+        <v>331</v>
+      </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="Q22" t="s">
         <v>59</v>
@@ -6081,13 +7244,13 @@
         <v>62</v>
       </c>
       <c r="V22" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="W22" t="s">
         <v>63</v>
       </c>
       <c r="X22" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="Y22" t="s">
         <v>64</v>
@@ -6099,46 +7262,49 @@
         <v>54</v>
       </c>
       <c r="AB22" s="1">
-        <v>46073.492824074077</v>
+        <v>46087.325694444444</v>
       </c>
       <c r="AC22" t="s">
         <v>65</v>
       </c>
       <c r="AD22" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE22" t="s">
         <v>64</v>
       </c>
       <c r="AF22" t="s">
         <v>64</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>336</v>
       </c>
       <c r="AH22" t="s">
         <v>66</v>
       </c>
       <c r="AI22" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="AJ22" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="AK22" t="s">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AL22" t="s">
         <v>67</v>
       </c>
       <c r="AM22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="AO22" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ22" t="s">
         <v>69</v>
@@ -6146,65 +7312,86 @@
       <c r="AR22" t="s">
         <v>70</v>
       </c>
-      <c r="AS22">
-        <v>256</v>
+      <c r="AT22" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>58</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>350</v>
       </c>
       <c r="AW22" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="AX22" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="AY22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AZ22" s="2">
-        <v>8192</v>
+        <v>4096</v>
       </c>
       <c r="BA22" t="s">
-        <v>160</v>
+        <v>201</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>202</v>
       </c>
       <c r="BD22" t="s">
-        <v>116</v>
+        <v>203</v>
+      </c>
+      <c r="BE22" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF22" t="s">
+        <v>202</v>
       </c>
       <c r="BG22" t="s">
-        <v>161</v>
+        <v>205</v>
+      </c>
+      <c r="BH22" t="s">
+        <v>424</v>
       </c>
       <c r="BI22" t="s">
-        <v>162</v>
+        <v>425</v>
       </c>
       <c r="BJ22" t="s">
-        <v>71</v>
+        <v>353</v>
       </c>
       <c r="BK22" t="b">
         <v>1</v>
       </c>
       <c r="BL22" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="BM22" t="s">
-        <v>83</v>
+        <v>426</v>
       </c>
       <c r="BN22" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="BO22" t="s">
+        <v>207</v>
+      </c>
+      <c r="BP22" t="s">
         <v>64</v>
       </c>
       <c r="BQ22" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR22" t="s">
         <v>53</v>
       </c>
-      <c r="BR22" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS22" s="1">
-        <v>46070.841192129628</v>
-      </c>
-      <c r="BT22" t="s">
-        <v>84</v>
+      <c r="BS22" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT22" s="1">
+        <v>46088.834722222222</v>
       </c>
       <c r="BU22" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="BV22" t="s">
         <v>64</v>
@@ -6213,36 +7400,51 @@
         <v>64</v>
       </c>
       <c r="BX22" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY22" t="s">
         <v>66</v>
       </c>
-      <c r="BY22" t="s">
+      <c r="BZ22" t="s">
         <v>70</v>
       </c>
-      <c r="BZ22">
-        <v>16</v>
-      </c>
-      <c r="CD22">
+      <c r="CA22">
+        <v>130</v>
+      </c>
+      <c r="CB22">
         <v>2</v>
       </c>
-      <c r="CF22" s="2">
-        <v>8192</v>
+      <c r="CE22">
+        <v>2</v>
+      </c>
+      <c r="CG22" s="2">
+        <v>4096</v>
       </c>
       <c r="CJ22" t="s">
-        <v>158</v>
-      </c>
-      <c r="CK22" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="CL22" t="s">
-        <v>341</v>
+        <v>360</v>
+      </c>
+      <c r="CN22" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO22" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="CP22" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="23" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B23" t="s">
-        <v>184</v>
+        <v>179</v>
+      </c>
+      <c r="C23" t="s">
+        <v>330</v>
       </c>
       <c r="D23" t="s">
         <v>53</v>
@@ -6251,16 +7453,16 @@
         <v>54</v>
       </c>
       <c r="F23" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G23" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H23" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I23" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J23" t="s">
         <v>55</v>
@@ -6277,8 +7479,11 @@
       <c r="N23" t="s">
         <v>58</v>
       </c>
+      <c r="O23" t="s">
+        <v>331</v>
+      </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q23" t="s">
         <v>59</v>
@@ -6296,13 +7501,13 @@
         <v>62</v>
       </c>
       <c r="V23" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="W23" t="s">
         <v>63</v>
       </c>
       <c r="X23" t="s">
-        <v>323</v>
+        <v>428</v>
       </c>
       <c r="Y23" t="s">
         <v>64</v>
@@ -6314,10 +7519,10 @@
         <v>54</v>
       </c>
       <c r="AB23" s="1">
-        <v>46073.490532407406</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC23" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD23" t="s">
         <v>64</v>
@@ -6327,18 +7532,21 @@
       </c>
       <c r="AF23" t="s">
         <v>64</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>330</v>
       </c>
       <c r="AH23" t="s">
         <v>66</v>
       </c>
       <c r="AI23" t="s">
-        <v>93</v>
+        <v>429</v>
       </c>
       <c r="AJ23">
-        <v>24.04</v>
+        <v>20.04</v>
       </c>
       <c r="AK23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL23" t="s">
         <v>67</v>
@@ -6347,77 +7555,92 @@
         <v>68</v>
       </c>
       <c r="AN23" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="AO23" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AP23">
         <v>1</v>
       </c>
       <c r="AQ23" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AR23" t="s">
         <v>70</v>
       </c>
       <c r="AS23">
-        <v>256</v>
+        <v>54</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>331</v>
       </c>
       <c r="AW23" t="s">
-        <v>323</v>
+        <v>428</v>
       </c>
       <c r="AX23" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="AZ23" s="2">
-        <v>7944</v>
+        <v>3909</v>
       </c>
       <c r="BA23" t="s">
-        <v>326</v>
+        <v>430</v>
+      </c>
+      <c r="BC23" t="s">
+        <v>202</v>
       </c>
       <c r="BD23" t="s">
-        <v>327</v>
+        <v>370</v>
+      </c>
+      <c r="BE23" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF23" t="s">
+        <v>202</v>
       </c>
       <c r="BG23" t="s">
-        <v>328</v>
+        <v>309</v>
+      </c>
+      <c r="BH23" t="s">
+        <v>363</v>
       </c>
       <c r="BI23" t="s">
-        <v>329</v>
+        <v>431</v>
       </c>
       <c r="BJ23" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK23" t="b">
         <v>1</v>
       </c>
       <c r="BL23" t="s">
+        <v>310</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO23" t="s">
+        <v>306</v>
+      </c>
+      <c r="BP23" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ23" t="s">
         <v>330</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BR23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS23" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT23" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU23" t="s">
         <v>83</v>
       </c>
-      <c r="BN23" t="s">
-        <v>323</v>
-      </c>
-      <c r="BO23" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ23" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR23" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS23" s="1">
-        <v>46070.841284722221</v>
-      </c>
-      <c r="BT23" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU23" t="s">
-        <v>64</v>
-      </c>
       <c r="BV23" t="s">
         <v>64</v>
       </c>
@@ -6425,36 +7648,51 @@
         <v>64</v>
       </c>
       <c r="BX23" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY23" t="s">
         <v>66</v>
       </c>
-      <c r="BY23" t="s">
+      <c r="BZ23" t="s">
         <v>70</v>
       </c>
-      <c r="BZ23">
-        <v>16</v>
-      </c>
-      <c r="CD23">
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CE23">
         <v>2</v>
       </c>
-      <c r="CF23" s="2">
-        <v>8192</v>
+      <c r="CG23" s="2">
+        <v>4096</v>
       </c>
       <c r="CJ23" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="CK23" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL23" t="s">
-        <v>340</v>
+        <v>308</v>
+      </c>
+      <c r="CM23" t="s">
+        <v>432</v>
+      </c>
+      <c r="CN23" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO23" t="s">
+        <v>433</v>
+      </c>
+      <c r="CP23" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="24" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>153</v>
+        <v>295</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>179</v>
+      </c>
+      <c r="C24" t="s">
+        <v>362</v>
       </c>
       <c r="D24" t="s">
         <v>53</v>
@@ -6463,16 +7701,16 @@
         <v>54</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="G24" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="H24" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="I24" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="J24" t="s">
         <v>55</v>
@@ -6481,7 +7719,7 @@
         <v>56</v>
       </c>
       <c r="L24" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="M24" t="s">
         <v>58</v>
@@ -6489,8 +7727,11 @@
       <c r="N24" t="s">
         <v>58</v>
       </c>
+      <c r="O24" t="s">
+        <v>331</v>
+      </c>
       <c r="P24" t="s">
-        <v>154</v>
+        <v>296</v>
       </c>
       <c r="Q24" t="s">
         <v>59</v>
@@ -6508,13 +7749,13 @@
         <v>62</v>
       </c>
       <c r="V24" t="s">
-        <v>155</v>
+        <v>297</v>
       </c>
       <c r="W24" t="s">
         <v>63</v>
       </c>
       <c r="X24" t="s">
-        <v>164</v>
+        <v>298</v>
       </c>
       <c r="Y24" t="s">
         <v>64</v>
@@ -6526,110 +7767,128 @@
         <v>54</v>
       </c>
       <c r="AB24" s="1">
-        <v>46073.506898148145</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC24" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD24" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE24" t="s">
         <v>64</v>
       </c>
       <c r="AF24" t="s">
         <v>64</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>362</v>
       </c>
       <c r="AH24" t="s">
         <v>66</v>
       </c>
       <c r="AI24" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ24">
-        <v>8.1</v>
+        <v>227</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>199</v>
       </c>
       <c r="AK24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL24" t="s">
         <v>67</v>
       </c>
       <c r="AM24" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="AO24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP24">
         <v>1</v>
       </c>
       <c r="AQ24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR24" t="s">
         <v>70</v>
       </c>
       <c r="AS24">
-        <v>64</v>
+        <v>128</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>331</v>
       </c>
       <c r="AW24" t="s">
-        <v>164</v>
+        <v>298</v>
       </c>
       <c r="AX24" t="s">
-        <v>166</v>
+        <v>300</v>
+      </c>
+      <c r="AY24" t="s">
+        <v>81</v>
       </c>
       <c r="AZ24" s="2">
-        <v>3661</v>
+        <v>8191</v>
       </c>
       <c r="BA24" t="s">
-        <v>167</v>
+        <v>301</v>
+      </c>
+      <c r="BC24" t="s">
+        <v>202</v>
       </c>
       <c r="BD24" t="s">
-        <v>86</v>
+        <v>290</v>
+      </c>
+      <c r="BE24" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>202</v>
       </c>
       <c r="BG24" t="s">
-        <v>168</v>
+        <v>302</v>
       </c>
       <c r="BI24" t="s">
-        <v>169</v>
+        <v>303</v>
       </c>
       <c r="BJ24" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK24" t="b">
         <v>1</v>
       </c>
       <c r="BL24" t="s">
-        <v>170</v>
-      </c>
-      <c r="BM24" t="s">
+        <v>304</v>
+      </c>
+      <c r="BN24" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO24" t="s">
+        <v>305</v>
+      </c>
+      <c r="BP24" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ24" t="s">
+        <v>362</v>
+      </c>
+      <c r="BR24" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS24" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT24" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU24" t="s">
         <v>83</v>
       </c>
-      <c r="BN24" t="s">
-        <v>171</v>
-      </c>
-      <c r="BO24" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ24" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR24" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS24" s="1">
-        <v>46072.839224537034</v>
-      </c>
-      <c r="BT24" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU24" t="s">
-        <v>64</v>
-      </c>
       <c r="BV24" t="s">
         <v>64</v>
       </c>
@@ -6637,36 +7896,51 @@
         <v>64</v>
       </c>
       <c r="BX24" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY24" t="s">
         <v>66</v>
       </c>
-      <c r="BY24" t="s">
+      <c r="BZ24" t="s">
         <v>70</v>
       </c>
-      <c r="BZ24">
+      <c r="CA24">
         <v>0</v>
       </c>
-      <c r="CD24">
+      <c r="CE24">
         <v>2</v>
       </c>
-      <c r="CF24" s="2">
-        <v>4096</v>
+      <c r="CG24" s="2">
+        <v>8192</v>
       </c>
       <c r="CJ24" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="CK24" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL24" t="s">
-        <v>341</v>
+        <v>299</v>
+      </c>
+      <c r="CM24" t="s">
+        <v>434</v>
+      </c>
+      <c r="CN24" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO24" t="s">
+        <v>435</v>
+      </c>
+      <c r="CP24" t="s">
+        <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>330</v>
       </c>
       <c r="D25" t="s">
         <v>53</v>
@@ -6675,16 +7949,16 @@
         <v>54</v>
       </c>
       <c r="F25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J25" t="s">
         <v>55</v>
@@ -6701,8 +7975,11 @@
       <c r="N25" t="s">
         <v>58</v>
       </c>
+      <c r="O25" t="s">
+        <v>331</v>
+      </c>
       <c r="P25" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="Q25" t="s">
         <v>59</v>
@@ -6720,13 +7997,13 @@
         <v>62</v>
       </c>
       <c r="V25" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="W25" t="s">
         <v>63</v>
       </c>
       <c r="X25" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="Y25" t="s">
         <v>64</v>
@@ -6738,92 +8015,128 @@
         <v>54</v>
       </c>
       <c r="AB25" s="1">
-        <v>46068.231145833335</v>
+        <v>46089.23333333333</v>
       </c>
       <c r="AC25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD25" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE25" t="s">
         <v>64</v>
       </c>
       <c r="AF25" t="s">
         <v>64</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>330</v>
       </c>
       <c r="AH25" t="s">
         <v>66</v>
       </c>
       <c r="AI25" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ25">
-        <v>7.9</v>
+        <v>152</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>77</v>
       </c>
       <c r="AL25" t="s">
         <v>67</v>
       </c>
       <c r="AM25" t="s">
-        <v>68</v>
+        <v>78</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>153</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>84</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>69</v>
       </c>
       <c r="AR25" t="s">
         <v>70</v>
       </c>
       <c r="AS25">
-        <v>64</v>
+        <v>256</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>331</v>
       </c>
       <c r="AW25" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="AX25" t="s">
-        <v>173</v>
+        <v>154</v>
+      </c>
+      <c r="AY25" t="s">
+        <v>81</v>
       </c>
       <c r="AZ25" s="2">
-        <v>4096</v>
+        <v>8192</v>
       </c>
       <c r="BA25" t="s">
-        <v>174</v>
+        <v>155</v>
+      </c>
+      <c r="BC25" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD25" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE25" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF25" t="s">
+        <v>202</v>
       </c>
       <c r="BG25" t="s">
-        <v>175</v>
+        <v>156</v>
+      </c>
+      <c r="BI25" t="s">
+        <v>157</v>
       </c>
       <c r="BJ25" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK25" t="b">
         <v>1</v>
       </c>
       <c r="BL25" t="s">
-        <v>176</v>
-      </c>
-      <c r="BM25" t="s">
+        <v>158</v>
+      </c>
+      <c r="BN25" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO25" t="s">
+        <v>151</v>
+      </c>
+      <c r="BP25" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ25" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR25" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS25" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT25" s="1">
+        <v>46089.313194444447</v>
+      </c>
+      <c r="BU25" t="s">
         <v>83</v>
       </c>
-      <c r="BN25" t="s">
-        <v>172</v>
-      </c>
-      <c r="BO25" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ25" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR25" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS25" s="1">
-        <v>46068.311215277776</v>
-      </c>
-      <c r="BT25" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU25" t="s">
-        <v>64</v>
-      </c>
       <c r="BV25" t="s">
         <v>64</v>
       </c>
@@ -6831,36 +8144,51 @@
         <v>64</v>
       </c>
       <c r="BX25" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY25" t="s">
         <v>66</v>
       </c>
-      <c r="BY25" t="s">
+      <c r="BZ25" t="s">
         <v>70</v>
       </c>
-      <c r="BZ25">
-        <v>0</v>
-      </c>
-      <c r="CD25">
+      <c r="CA25">
+        <v>16</v>
+      </c>
+      <c r="CE25">
         <v>2</v>
       </c>
-      <c r="CF25" s="2">
-        <v>4096</v>
+      <c r="CG25" s="2">
+        <v>8192</v>
       </c>
       <c r="CJ25" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="CK25" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL25" t="s">
-        <v>341</v>
+        <v>153</v>
+      </c>
+      <c r="CM25" t="s">
+        <v>436</v>
+      </c>
+      <c r="CN25" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO25" t="s">
+        <v>437</v>
+      </c>
+      <c r="CP25" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="26" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="C26" t="s">
+        <v>336</v>
       </c>
       <c r="D26" t="s">
         <v>53</v>
@@ -6869,16 +8197,16 @@
         <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J26" t="s">
         <v>55</v>
@@ -6895,8 +8223,11 @@
       <c r="N26" t="s">
         <v>58</v>
       </c>
+      <c r="O26" t="s">
+        <v>331</v>
+      </c>
       <c r="P26" t="s">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="Q26" t="s">
         <v>59</v>
@@ -6914,13 +8245,13 @@
         <v>62</v>
       </c>
       <c r="V26" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="W26" t="s">
         <v>63</v>
       </c>
       <c r="X26" t="s">
-        <v>177</v>
+        <v>438</v>
       </c>
       <c r="Y26" t="s">
         <v>64</v>
@@ -6932,10 +8263,10 @@
         <v>54</v>
       </c>
       <c r="AB26" s="1">
-        <v>46068.231145833335</v>
+        <v>46089.232638888891</v>
       </c>
       <c r="AC26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD26" t="s">
         <v>64</v>
@@ -6945,15 +8276,21 @@
       </c>
       <c r="AF26" t="s">
         <v>64</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>336</v>
       </c>
       <c r="AH26" t="s">
         <v>66</v>
       </c>
       <c r="AI26" t="s">
-        <v>121</v>
+        <v>439</v>
       </c>
       <c r="AJ26">
-        <v>7.9</v>
+        <v>6.1</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>77</v>
       </c>
       <c r="AL26" t="s">
         <v>67</v>
@@ -6961,8 +8298,17 @@
       <c r="AM26" t="s">
         <v>68</v>
       </c>
+      <c r="AN26" t="s">
+        <v>119</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>79</v>
+      </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>80</v>
       </c>
       <c r="AR26" t="s">
         <v>70</v>
@@ -6970,54 +8316,75 @@
       <c r="AS26">
         <v>64</v>
       </c>
+      <c r="AV26" t="s">
+        <v>331</v>
+      </c>
       <c r="AW26" t="s">
-        <v>177</v>
+        <v>438</v>
       </c>
       <c r="AX26" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="AZ26" s="2">
-        <v>4096</v>
+        <v>3961</v>
       </c>
       <c r="BA26" t="s">
-        <v>179</v>
+        <v>440</v>
+      </c>
+      <c r="BC26" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>370</v>
+      </c>
+      <c r="BE26" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF26" t="s">
+        <v>202</v>
       </c>
       <c r="BG26" t="s">
-        <v>180</v>
+        <v>120</v>
+      </c>
+      <c r="BH26" t="s">
+        <v>363</v>
+      </c>
+      <c r="BI26" t="s">
+        <v>441</v>
       </c>
       <c r="BJ26" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK26" t="b">
         <v>1</v>
       </c>
       <c r="BL26" t="s">
-        <v>181</v>
-      </c>
-      <c r="BM26" t="s">
+        <v>121</v>
+      </c>
+      <c r="BN26" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO26" t="s">
+        <v>117</v>
+      </c>
+      <c r="BP26" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ26" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR26" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS26" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT26" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU26" t="s">
         <v>83</v>
       </c>
-      <c r="BN26" t="s">
-        <v>177</v>
-      </c>
-      <c r="BO26" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ26" t="s">
-        <v>53</v>
-      </c>
-      <c r="BR26" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS26" s="1">
-        <v>46068.311215277776</v>
-      </c>
-      <c r="BT26" t="s">
-        <v>84</v>
-      </c>
-      <c r="BU26" t="s">
-        <v>64</v>
-      </c>
       <c r="BV26" t="s">
         <v>64</v>
       </c>
@@ -7025,36 +8392,51 @@
         <v>64</v>
       </c>
       <c r="BX26" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY26" t="s">
         <v>66</v>
       </c>
-      <c r="BY26" t="s">
+      <c r="BZ26" t="s">
         <v>70</v>
       </c>
-      <c r="BZ26">
+      <c r="CA26">
         <v>0</v>
       </c>
-      <c r="CD26">
+      <c r="CE26">
         <v>2</v>
       </c>
-      <c r="CF26" s="2">
+      <c r="CG26" s="2">
         <v>4096</v>
       </c>
       <c r="CJ26" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="CK26" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL26" t="s">
-        <v>341</v>
+        <v>119</v>
+      </c>
+      <c r="CM26" t="s">
+        <v>442</v>
+      </c>
+      <c r="CN26" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO26" t="s">
+        <v>443</v>
+      </c>
+      <c r="CP26" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="27" spans="1:90" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>306</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>184</v>
+        <v>76</v>
+      </c>
+      <c r="C27" t="s">
+        <v>336</v>
       </c>
       <c r="D27" t="s">
         <v>53</v>
@@ -7063,16 +8445,16 @@
         <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>185</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="H27" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="I27" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="J27" t="s">
         <v>55</v>
@@ -7081,7 +8463,7 @@
         <v>56</v>
       </c>
       <c r="L27" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="M27" t="s">
         <v>58</v>
@@ -7089,8 +8471,11 @@
       <c r="N27" t="s">
         <v>58</v>
       </c>
+      <c r="O27" t="s">
+        <v>331</v>
+      </c>
       <c r="P27" t="s">
-        <v>307</v>
+        <v>89</v>
       </c>
       <c r="Q27" t="s">
         <v>59</v>
@@ -7108,13 +8493,13 @@
         <v>62</v>
       </c>
       <c r="V27" t="s">
-        <v>308</v>
+        <v>90</v>
       </c>
       <c r="W27" t="s">
         <v>63</v>
       </c>
       <c r="X27" t="s">
-        <v>331</v>
+        <v>107</v>
       </c>
       <c r="Y27" t="s">
         <v>64</v>
@@ -7126,143 +8511,1643 @@
         <v>54</v>
       </c>
       <c r="AB27" s="1">
-        <v>46073.492824074077</v>
+        <v>46089.23333333333</v>
       </c>
       <c r="AC27" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AD27" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="AE27" t="s">
         <v>64</v>
       </c>
       <c r="AF27" t="s">
         <v>64</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>336</v>
       </c>
       <c r="AH27" t="s">
         <v>66</v>
       </c>
       <c r="AI27" t="s">
-        <v>332</v>
-      </c>
-      <c r="AJ27">
-        <v>22.04</v>
+        <v>108</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>109</v>
       </c>
       <c r="AK27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s">
         <v>67</v>
       </c>
       <c r="AM27" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="AN27" t="s">
-        <v>333</v>
+        <v>110</v>
       </c>
       <c r="AO27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AP27">
         <v>1</v>
       </c>
       <c r="AQ27" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="AR27" t="s">
         <v>70</v>
       </c>
       <c r="AS27">
-        <v>54</v>
+        <v>256</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>331</v>
       </c>
       <c r="AW27" t="s">
-        <v>331</v>
+        <v>107</v>
       </c>
       <c r="AX27" t="s">
-        <v>334</v>
+        <v>111</v>
+      </c>
+      <c r="AY27" t="s">
+        <v>81</v>
       </c>
       <c r="AZ27" s="2">
-        <v>3914</v>
+        <v>8192</v>
       </c>
       <c r="BA27" t="s">
-        <v>335</v>
+        <v>112</v>
+      </c>
+      <c r="BC27" t="s">
+        <v>202</v>
       </c>
       <c r="BD27" t="s">
-        <v>86</v>
+        <v>113</v>
+      </c>
+      <c r="BE27" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF27" t="s">
+        <v>202</v>
       </c>
       <c r="BG27" t="s">
-        <v>336</v>
+        <v>114</v>
       </c>
       <c r="BI27" t="s">
-        <v>337</v>
+        <v>115</v>
       </c>
       <c r="BJ27" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="BK27" t="b">
         <v>1</v>
       </c>
       <c r="BL27" t="s">
-        <v>338</v>
-      </c>
-      <c r="BM27" t="s">
+        <v>116</v>
+      </c>
+      <c r="BN27" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO27" t="s">
+        <v>107</v>
+      </c>
+      <c r="BP27" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ27" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR27" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS27" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT27" s="1">
+        <v>46089.313194444447</v>
+      </c>
+      <c r="BU27" t="s">
         <v>83</v>
       </c>
-      <c r="BN27" t="s">
-        <v>339</v>
-      </c>
-      <c r="BO27" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ27" t="s">
+      <c r="BV27" t="s">
+        <v>64</v>
+      </c>
+      <c r="BW27" t="s">
+        <v>64</v>
+      </c>
+      <c r="BX27" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY27" t="s">
+        <v>66</v>
+      </c>
+      <c r="BZ27" t="s">
+        <v>70</v>
+      </c>
+      <c r="CA27">
+        <v>16</v>
+      </c>
+      <c r="CE27">
+        <v>2</v>
+      </c>
+      <c r="CG27" s="2">
+        <v>8192</v>
+      </c>
+      <c r="CJ27" t="s">
+        <v>204</v>
+      </c>
+      <c r="CK27" t="s">
+        <v>110</v>
+      </c>
+      <c r="CM27" t="s">
+        <v>444</v>
+      </c>
+      <c r="CN27" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO27" t="s">
+        <v>445</v>
+      </c>
+      <c r="CP27" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" spans="1:94" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s">
+        <v>362</v>
+      </c>
+      <c r="D28" t="s">
         <v>53</v>
       </c>
-      <c r="BR27" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS27" s="1">
-        <v>46072.839085648149</v>
-      </c>
-      <c r="BT27" t="s">
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" t="s">
+        <v>76</v>
+      </c>
+      <c r="J28" t="s">
+        <v>55</v>
+      </c>
+      <c r="K28" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" t="s">
+        <v>70</v>
+      </c>
+      <c r="M28" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" t="s">
+        <v>58</v>
+      </c>
+      <c r="O28" t="s">
+        <v>331</v>
+      </c>
+      <c r="P28" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>59</v>
+      </c>
+      <c r="R28" t="s">
+        <v>60</v>
+      </c>
+      <c r="S28" t="s">
+        <v>60</v>
+      </c>
+      <c r="T28" t="s">
+        <v>61</v>
+      </c>
+      <c r="U28" t="s">
+        <v>62</v>
+      </c>
+      <c r="V28" t="s">
+        <v>124</v>
+      </c>
+      <c r="W28" t="s">
+        <v>63</v>
+      </c>
+      <c r="X28" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>46089.232638888891</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>362</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ28">
+        <v>15.6</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP28">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS28">
+        <v>30</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU28" t="s">
+        <v>58</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>331</v>
+      </c>
+      <c r="AW28" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX28" t="s">
+        <v>133</v>
+      </c>
+      <c r="AZ28" s="2">
+        <v>3624</v>
+      </c>
+      <c r="BA28" t="s">
+        <v>134</v>
+      </c>
+      <c r="BC28" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD28" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE28" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF28" t="s">
+        <v>202</v>
+      </c>
+      <c r="BG28" t="s">
+        <v>136</v>
+      </c>
+      <c r="BI28" t="s">
+        <v>137</v>
+      </c>
+      <c r="BJ28" t="s">
+        <v>333</v>
+      </c>
+      <c r="BK28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL28" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN28" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO28" t="s">
+        <v>139</v>
+      </c>
+      <c r="BP28" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ28" t="s">
+        <v>362</v>
+      </c>
+      <c r="BR28" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS28" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT28" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU28" t="s">
+        <v>83</v>
+      </c>
+      <c r="BV28" t="s">
+        <v>64</v>
+      </c>
+      <c r="BW28" t="s">
+        <v>64</v>
+      </c>
+      <c r="BX28" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY28" t="s">
+        <v>66</v>
+      </c>
+      <c r="BZ28" t="s">
+        <v>70</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CC28" t="s">
+        <v>58</v>
+      </c>
+      <c r="CD28" t="s">
+        <v>58</v>
+      </c>
+      <c r="CE28">
+        <v>2</v>
+      </c>
+      <c r="CG28" s="2">
+        <v>4096</v>
+      </c>
+      <c r="CJ28" t="s">
+        <v>204</v>
+      </c>
+      <c r="CK28" t="s">
+        <v>132</v>
+      </c>
+      <c r="CM28" t="s">
+        <v>446</v>
+      </c>
+      <c r="CN28" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO28" t="s">
+        <v>447</v>
+      </c>
+      <c r="CP28" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="29" spans="1:94" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>336</v>
+      </c>
+      <c r="D29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" t="s">
+        <v>223</v>
+      </c>
+      <c r="G29" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" t="s">
+        <v>76</v>
+      </c>
+      <c r="J29" t="s">
+        <v>55</v>
+      </c>
+      <c r="K29" t="s">
+        <v>56</v>
+      </c>
+      <c r="L29" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O29" t="s">
+        <v>331</v>
+      </c>
+      <c r="P29" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>59</v>
+      </c>
+      <c r="R29" t="s">
+        <v>60</v>
+      </c>
+      <c r="S29" t="s">
+        <v>60</v>
+      </c>
+      <c r="T29" t="s">
+        <v>61</v>
+      </c>
+      <c r="U29" t="s">
+        <v>62</v>
+      </c>
+      <c r="V29" t="s">
+        <v>225</v>
+      </c>
+      <c r="W29" t="s">
+        <v>63</v>
+      </c>
+      <c r="X29" t="s">
+        <v>448</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB29" s="1">
+        <v>46089.232638888891</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>336</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>392</v>
+      </c>
+      <c r="AJ29">
+        <v>9.5</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>449</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP29">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS29">
+        <v>64</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>331</v>
+      </c>
+      <c r="AW29" t="s">
+        <v>448</v>
+      </c>
+      <c r="AX29" t="s">
+        <v>450</v>
+      </c>
+      <c r="AZ29" s="2">
+        <v>3459</v>
+      </c>
+      <c r="BA29" t="s">
+        <v>451</v>
+      </c>
+      <c r="BC29" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD29" t="s">
+        <v>342</v>
+      </c>
+      <c r="BE29" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF29" t="s">
+        <v>202</v>
+      </c>
+      <c r="BG29" t="s">
+        <v>452</v>
+      </c>
+      <c r="BI29" t="s">
+        <v>453</v>
+      </c>
+      <c r="BJ29" t="s">
+        <v>333</v>
+      </c>
+      <c r="BK29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL29" t="s">
+        <v>454</v>
+      </c>
+      <c r="BN29" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO29" t="s">
+        <v>455</v>
+      </c>
+      <c r="BP29" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ29" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR29" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS29" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT29" s="1">
+        <v>46089.31527777778</v>
+      </c>
+      <c r="BU29" t="s">
+        <v>83</v>
+      </c>
+      <c r="BV29" t="s">
+        <v>64</v>
+      </c>
+      <c r="BW29" t="s">
+        <v>64</v>
+      </c>
+      <c r="BX29" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY29" t="s">
+        <v>66</v>
+      </c>
+      <c r="BZ29" t="s">
+        <v>70</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CE29">
+        <v>2</v>
+      </c>
+      <c r="CG29" s="2">
+        <v>4096</v>
+      </c>
+      <c r="CJ29" t="s">
+        <v>204</v>
+      </c>
+      <c r="CK29" t="s">
+        <v>449</v>
+      </c>
+      <c r="CM29" t="s">
+        <v>456</v>
+      </c>
+      <c r="CN29" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO29" t="s">
+        <v>457</v>
+      </c>
+      <c r="CP29" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="30" spans="1:94" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>222</v>
+      </c>
+      <c r="B30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" t="s">
+        <v>336</v>
+      </c>
+      <c r="D30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" t="s">
+        <v>223</v>
+      </c>
+      <c r="G30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" t="s">
+        <v>76</v>
+      </c>
+      <c r="J30" t="s">
+        <v>55</v>
+      </c>
+      <c r="K30" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" t="s">
+        <v>58</v>
+      </c>
+      <c r="O30" t="s">
+        <v>331</v>
+      </c>
+      <c r="P30" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>59</v>
+      </c>
+      <c r="R30" t="s">
+        <v>60</v>
+      </c>
+      <c r="S30" t="s">
+        <v>60</v>
+      </c>
+      <c r="T30" t="s">
+        <v>61</v>
+      </c>
+      <c r="U30" t="s">
+        <v>62</v>
+      </c>
+      <c r="V30" t="s">
+        <v>225</v>
+      </c>
+      <c r="W30" t="s">
+        <v>63</v>
+      </c>
+      <c r="X30" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB30" s="1">
+        <v>46089.23333333333</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>336</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>184</v>
+      </c>
+      <c r="AJ30">
+        <v>9.6</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>246</v>
+      </c>
+      <c r="AO30" t="s">
         <v>84</v>
       </c>
-      <c r="BU27" t="s">
-        <v>64</v>
-      </c>
-      <c r="BV27" t="s">
-        <v>64</v>
-      </c>
-      <c r="BW27" t="s">
-        <v>64</v>
-      </c>
-      <c r="BX27" t="s">
+      <c r="AP30">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS30">
+        <v>256</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>331</v>
+      </c>
+      <c r="AW30" t="s">
+        <v>245</v>
+      </c>
+      <c r="AX30" t="s">
+        <v>247</v>
+      </c>
+      <c r="AZ30" s="2">
+        <v>7682</v>
+      </c>
+      <c r="BA30" t="s">
+        <v>248</v>
+      </c>
+      <c r="BC30" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD30" t="s">
+        <v>249</v>
+      </c>
+      <c r="BE30" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF30" t="s">
+        <v>202</v>
+      </c>
+      <c r="BG30" t="s">
+        <v>250</v>
+      </c>
+      <c r="BI30" t="s">
+        <v>251</v>
+      </c>
+      <c r="BJ30" t="s">
+        <v>333</v>
+      </c>
+      <c r="BK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL30" t="s">
+        <v>252</v>
+      </c>
+      <c r="BN30" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO30" t="s">
+        <v>245</v>
+      </c>
+      <c r="BP30" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ30" t="s">
+        <v>336</v>
+      </c>
+      <c r="BR30" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS30" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT30" s="1">
+        <v>46089.313194444447</v>
+      </c>
+      <c r="BU30" t="s">
+        <v>83</v>
+      </c>
+      <c r="BV30" t="s">
+        <v>64</v>
+      </c>
+      <c r="BW30" t="s">
+        <v>64</v>
+      </c>
+      <c r="BX30" t="s">
+        <v>64</v>
+      </c>
+      <c r="BY30" t="s">
         <v>66</v>
       </c>
-      <c r="BY27" t="s">
+      <c r="BZ30" t="s">
         <v>70</v>
       </c>
-      <c r="BZ27">
-        <v>0</v>
-      </c>
-      <c r="CD27">
+      <c r="CA30">
+        <v>16</v>
+      </c>
+      <c r="CE30">
         <v>2</v>
       </c>
-      <c r="CF27" s="2">
-        <v>4096</v>
-      </c>
-      <c r="CJ27" t="s">
-        <v>333</v>
-      </c>
-      <c r="CK27" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL27" t="s">
-        <v>340</v>
+      <c r="CG30" s="2">
+        <v>8192</v>
+      </c>
+      <c r="CJ30" t="s">
+        <v>204</v>
+      </c>
+      <c r="CK30" t="s">
+        <v>246</v>
+      </c>
+      <c r="CM30" t="s">
+        <v>458</v>
+      </c>
+      <c r="CN30" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO30" t="s">
+        <v>459</v>
+      </c>
+      <c r="CP30" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:94" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>253</v>
+      </c>
+      <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s">
+        <v>362</v>
+      </c>
+      <c r="D31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" t="s">
+        <v>223</v>
+      </c>
+      <c r="G31" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K31" t="s">
+        <v>56</v>
+      </c>
+      <c r="L31" t="s">
+        <v>70</v>
+      </c>
+      <c r="M31" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" t="s">
+        <v>58</v>
+      </c>
+      <c r="O31" t="s">
+        <v>331</v>
+      </c>
+      <c r="P31" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>59</v>
+      </c>
+      <c r="R31" t="s">
+        <v>60</v>
+      </c>
+      <c r="S31" t="s">
+        <v>60</v>
+      </c>
+      <c r="T31" t="s">
+        <v>61</v>
+      </c>
+      <c r="U31" t="s">
+        <v>62</v>
+      </c>
+      <c r="V31" t="s">
+        <v>255</v>
+      </c>
+      <c r="W31" t="s">
+        <v>63</v>
+      </c>
+      <c r="X31" t="s">
+        <v>460</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB31" s="1">
+        <v>46087.322916666664</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>362</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>257</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>258</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>185</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO31" t="s">
+        <v>186</v>
+      </c>
+      <c r="AP31">
+        <v>2</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>70</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>350</v>
+      </c>
+      <c r="AW31" t="s">
+        <v>460</v>
+      </c>
+      <c r="AX31" t="s">
+        <v>461</v>
+      </c>
+      <c r="AY31" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ31" s="2">
+        <v>8192</v>
+      </c>
+      <c r="BA31" t="s">
+        <v>462</v>
+      </c>
+      <c r="BC31" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD31" t="s">
+        <v>463</v>
+      </c>
+      <c r="BE31" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF31" t="s">
+        <v>202</v>
+      </c>
+      <c r="BG31" t="s">
+        <v>464</v>
+      </c>
+      <c r="BI31" t="s">
+        <v>465</v>
+      </c>
+      <c r="BJ31" t="s">
+        <v>353</v>
+      </c>
+      <c r="BK31" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL31" t="s">
+        <v>466</v>
+      </c>
+      <c r="BN31" t="s">
+        <v>191</v>
+      </c>
+      <c r="BO31" t="s">
+        <v>467</v>
+      </c>
+      <c r="BP31" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ31" t="s">
+        <v>362</v>
+      </c>
+      <c r="BR31" t="s">
+        <v>468</v>
+      </c>
+      <c r="BS31" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT31" s="1">
+        <v>46089.15347222222</v>
+      </c>
+      <c r="BU31" t="s">
+        <v>469</v>
+      </c>
+      <c r="BV31" t="s">
+        <v>470</v>
+      </c>
+      <c r="BW31" t="s">
+        <v>64</v>
+      </c>
+      <c r="BX31" t="s">
+        <v>471</v>
+      </c>
+      <c r="BY31" t="s">
+        <v>66</v>
+      </c>
+      <c r="BZ31" t="s">
+        <v>70</v>
+      </c>
+      <c r="CA31">
+        <v>110</v>
+      </c>
+      <c r="CB31">
+        <v>2</v>
+      </c>
+      <c r="CE31">
+        <v>2</v>
+      </c>
+      <c r="CG31" s="2">
+        <v>8192</v>
+      </c>
+      <c r="CJ31" t="s">
+        <v>204</v>
+      </c>
+      <c r="CL31" t="s">
+        <v>360</v>
+      </c>
+      <c r="CN31" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO31" t="s">
+        <v>472</v>
+      </c>
+      <c r="CP31" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="32" spans="1:94" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>266</v>
+      </c>
+      <c r="B32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" t="s">
+        <v>330</v>
+      </c>
+      <c r="D32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" t="s">
+        <v>223</v>
+      </c>
+      <c r="G32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32" t="s">
+        <v>76</v>
+      </c>
+      <c r="J32" t="s">
+        <v>55</v>
+      </c>
+      <c r="K32" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" t="s">
+        <v>58</v>
+      </c>
+      <c r="O32" t="s">
+        <v>331</v>
+      </c>
+      <c r="P32" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>59</v>
+      </c>
+      <c r="R32" t="s">
+        <v>60</v>
+      </c>
+      <c r="S32" t="s">
+        <v>60</v>
+      </c>
+      <c r="T32" t="s">
+        <v>61</v>
+      </c>
+      <c r="U32" t="s">
+        <v>62</v>
+      </c>
+      <c r="V32" t="s">
+        <v>268</v>
+      </c>
+      <c r="W32" t="s">
+        <v>63</v>
+      </c>
+      <c r="X32" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB32" s="1">
+        <v>46087.322916666664</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>330</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>474</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>258</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>185</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>186</v>
+      </c>
+      <c r="AP32">
+        <v>2</v>
+      </c>
+      <c r="AQ32" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>70</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>350</v>
+      </c>
+      <c r="AW32" t="s">
+        <v>473</v>
+      </c>
+      <c r="AX32" t="s">
+        <v>475</v>
+      </c>
+      <c r="AY32" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ32" s="2">
+        <v>8192</v>
+      </c>
+      <c r="BA32" t="s">
+        <v>476</v>
+      </c>
+      <c r="BC32" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD32" t="s">
+        <v>463</v>
+      </c>
+      <c r="BE32" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF32" t="s">
+        <v>202</v>
+      </c>
+      <c r="BG32" t="s">
+        <v>477</v>
+      </c>
+      <c r="BI32" t="s">
+        <v>478</v>
+      </c>
+      <c r="BJ32" t="s">
+        <v>353</v>
+      </c>
+      <c r="BK32" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL32" t="s">
+        <v>479</v>
+      </c>
+      <c r="BN32" t="s">
+        <v>191</v>
+      </c>
+      <c r="BO32" t="s">
+        <v>480</v>
+      </c>
+      <c r="BP32" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ32" t="s">
+        <v>330</v>
+      </c>
+      <c r="BR32" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS32" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT32" s="1">
+        <v>46089.15347222222</v>
+      </c>
+      <c r="BU32" t="s">
+        <v>469</v>
+      </c>
+      <c r="BV32" t="s">
+        <v>470</v>
+      </c>
+      <c r="BW32" t="s">
+        <v>64</v>
+      </c>
+      <c r="BX32" t="s">
+        <v>471</v>
+      </c>
+      <c r="BY32" t="s">
+        <v>66</v>
+      </c>
+      <c r="BZ32" t="s">
+        <v>70</v>
+      </c>
+      <c r="CA32">
+        <v>110</v>
+      </c>
+      <c r="CB32">
+        <v>2</v>
+      </c>
+      <c r="CE32">
+        <v>2</v>
+      </c>
+      <c r="CG32" s="2">
+        <v>8192</v>
+      </c>
+      <c r="CJ32" t="s">
+        <v>204</v>
+      </c>
+      <c r="CL32" t="s">
+        <v>360</v>
+      </c>
+      <c r="CN32" t="s">
+        <v>54</v>
+      </c>
+      <c r="CO32" t="s">
+        <v>481</v>
+      </c>
+      <c r="CP32" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="F1:F32" xr:uid="{E1AF9D5F-633B-4593-A18F-1065DF67794C}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5D0EE1E-A799-4EFC-9C49-742675C7AFFA}">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.77734375" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
+        <v>327</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:B27" xr:uid="{E5D0EE1E-A799-4EFC-9C49-742675C7AFFA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/publish/data.xlsx
+++ b/src/publish/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bayer\Bayer.LoadData\Bayer.LoadODSData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\enademoproject\src\publish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A4E1B5-2A1E-4ECD-8FD9-A9F18622BBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D5D163-E035-41B3-830B-959DE10E0DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B258FCD-D826-42E0-B321-CB971A01F84A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$F$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$C$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$B$1:$B$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1898,7 +1898,7 @@
     <col min="21" max="21" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="31.77734375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.77734375" customWidth="1"/>
     <col min="25" max="25" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.5546875" bestFit="1" customWidth="1"/>
@@ -1913,6 +1913,8 @@
     <col min="40" max="40" width="47.44140625" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="35.88671875" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="45.109375" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="49.5546875" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -9914,7 +9916,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F32" xr:uid="{E1AF9D5F-633B-4593-A18F-1065DF67794C}"/>
+  <autoFilter ref="B1:C32" xr:uid="{E1AF9D5F-633B-4593-A18F-1065DF67794C}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
